--- a/Picking by Case ID.xlsx
+++ b/Picking by Case ID.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dsvcorp-my.sharepoint.com/personal/wendel_santos1_dsv_com/Documents/Documents/code/case-id-barcode-generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="51" documentId="8_{33C33F29-AEF1-4D5A-A65C-4D1749FCB150}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E5CC7117-493B-4C84-A8E8-0BB337863359}"/>
+  <xr:revisionPtr revIDLastSave="62" documentId="8_{33C33F29-AEF1-4D5A-A65C-4D1749FCB150}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22CC86CE-6DA2-4360-BBAB-1533359C8CF5}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="828" uniqueCount="310">
   <si>
     <t>Order Number</t>
   </si>
@@ -4365,7 +4365,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EE41E71-179D-477A-9226-D4B51EEC218A}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:B108"/>
+  <dimension ref="A1:B112"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -4714,23 +4714,23 @@
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>10226385</v>
+        <v>10226380</v>
       </c>
       <c r="B44" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>10226387</v>
+        <v>10226385</v>
       </c>
       <c r="B45" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>10226388</v>
+        <v>10226386</v>
       </c>
       <c r="B46" t="s">
         <v>140</v>
@@ -4738,7 +4738,7 @@
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>10226392</v>
+        <v>10226387</v>
       </c>
       <c r="B47" t="s">
         <v>140</v>
@@ -4746,7 +4746,7 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>10226396</v>
+        <v>10226388</v>
       </c>
       <c r="B48" t="s">
         <v>140</v>
@@ -4754,39 +4754,39 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>10226397</v>
+        <v>10226392</v>
       </c>
       <c r="B49" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>10226398</v>
+        <v>10226396</v>
       </c>
       <c r="B50" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>10226399</v>
+        <v>10226397</v>
       </c>
       <c r="B51" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>10226400</v>
+        <v>10226398</v>
       </c>
       <c r="B52" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>10226401</v>
+        <v>10226399</v>
       </c>
       <c r="B53" t="s">
         <v>140</v>
@@ -4794,39 +4794,39 @@
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>10226402</v>
+        <v>10226400</v>
       </c>
       <c r="B54" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>10226403</v>
+        <v>10226401</v>
       </c>
       <c r="B55" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>10226405</v>
+        <v>10226402</v>
       </c>
       <c r="B56" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>10226406</v>
+        <v>10226403</v>
       </c>
       <c r="B57" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>10226407</v>
+        <v>10226404</v>
       </c>
       <c r="B58" t="s">
         <v>140</v>
@@ -4834,15 +4834,15 @@
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>10226409</v>
+        <v>10226405</v>
       </c>
       <c r="B59" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>10226410</v>
+        <v>10226406</v>
       </c>
       <c r="B60" t="s">
         <v>140</v>
@@ -4850,7 +4850,7 @@
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>10226412</v>
+        <v>10226407</v>
       </c>
       <c r="B61" t="s">
         <v>140</v>
@@ -4858,15 +4858,15 @@
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>10226413</v>
+        <v>10226409</v>
       </c>
       <c r="B62" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>10226415</v>
+        <v>10226410</v>
       </c>
       <c r="B63" t="s">
         <v>140</v>
@@ -4874,15 +4874,15 @@
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>10226417</v>
+        <v>10226412</v>
       </c>
       <c r="B64" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>10226418</v>
+        <v>10226413</v>
       </c>
       <c r="B65" t="s">
         <v>140</v>
@@ -4890,23 +4890,23 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>10226420</v>
+        <v>10226415</v>
       </c>
       <c r="B66" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>10226421</v>
+        <v>10226417</v>
       </c>
       <c r="B67" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>10226422</v>
+        <v>10226418</v>
       </c>
       <c r="B68" t="s">
         <v>140</v>
@@ -4914,39 +4914,39 @@
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>10226425</v>
+        <v>10226420</v>
       </c>
       <c r="B69" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>10226427</v>
+        <v>10226421</v>
       </c>
       <c r="B70" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>10226429</v>
+        <v>10226422</v>
       </c>
       <c r="B71" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>10226430</v>
+        <v>10226425</v>
       </c>
       <c r="B72" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>10226431</v>
+        <v>10226427</v>
       </c>
       <c r="B73" t="s">
         <v>144</v>
@@ -4954,7 +4954,7 @@
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>10226432</v>
+        <v>10226429</v>
       </c>
       <c r="B74" t="s">
         <v>144</v>
@@ -4962,31 +4962,31 @@
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>10226435</v>
+        <v>10226430</v>
       </c>
       <c r="B75" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>10226437</v>
+        <v>10226431</v>
       </c>
       <c r="B76" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>10226438</v>
+        <v>10226432</v>
       </c>
       <c r="B77" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>10226439</v>
+        <v>10226435</v>
       </c>
       <c r="B78" t="s">
         <v>140</v>
@@ -4994,7 +4994,7 @@
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>10226441</v>
+        <v>10226437</v>
       </c>
       <c r="B79" t="s">
         <v>140</v>
@@ -5002,7 +5002,7 @@
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>10226442</v>
+        <v>10226438</v>
       </c>
       <c r="B80" t="s">
         <v>140</v>
@@ -5010,7 +5010,7 @@
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>10226444</v>
+        <v>10226439</v>
       </c>
       <c r="B81" t="s">
         <v>140</v>
@@ -5018,7 +5018,7 @@
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>10226445</v>
+        <v>10226441</v>
       </c>
       <c r="B82" t="s">
         <v>140</v>
@@ -5026,7 +5026,7 @@
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>10226446</v>
+        <v>10226442</v>
       </c>
       <c r="B83" t="s">
         <v>140</v>
@@ -5034,7 +5034,7 @@
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>10226447</v>
+        <v>10226444</v>
       </c>
       <c r="B84" t="s">
         <v>140</v>
@@ -5042,7 +5042,7 @@
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>10226453</v>
+        <v>10226445</v>
       </c>
       <c r="B85" t="s">
         <v>140</v>
@@ -5050,7 +5050,7 @@
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>10226454</v>
+        <v>10226446</v>
       </c>
       <c r="B86" t="s">
         <v>140</v>
@@ -5058,7 +5058,7 @@
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87">
-        <v>10226455</v>
+        <v>10226447</v>
       </c>
       <c r="B87" t="s">
         <v>140</v>
@@ -5066,31 +5066,31 @@
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>10226463</v>
+        <v>10226452</v>
       </c>
       <c r="B88" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>10226618</v>
+        <v>10226453</v>
       </c>
       <c r="B89" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>10226781</v>
+        <v>10226454</v>
       </c>
       <c r="B90" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>10227069</v>
+        <v>10226455</v>
       </c>
       <c r="B91" t="s">
         <v>140</v>
@@ -5098,7 +5098,7 @@
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>10227309</v>
+        <v>10226463</v>
       </c>
       <c r="B92" t="s">
         <v>144</v>
@@ -5106,7 +5106,7 @@
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>10227310</v>
+        <v>10226618</v>
       </c>
       <c r="B93" t="s">
         <v>144</v>
@@ -5114,23 +5114,23 @@
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>10227896</v>
+        <v>10226781</v>
       </c>
       <c r="B94" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>10230675</v>
+        <v>10227069</v>
       </c>
       <c r="B95" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>10231475</v>
+        <v>10227309</v>
       </c>
       <c r="B96" t="s">
         <v>144</v>
@@ -5138,7 +5138,7 @@
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97">
-        <v>10231484</v>
+        <v>10227310</v>
       </c>
       <c r="B97" t="s">
         <v>144</v>
@@ -5146,23 +5146,23 @@
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>10236617</v>
+        <v>10227896</v>
       </c>
       <c r="B98" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99">
-        <v>10236618</v>
+        <v>10230675</v>
       </c>
       <c r="B99" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>10236662</v>
+        <v>10231475</v>
       </c>
       <c r="B100" t="s">
         <v>144</v>
@@ -5170,7 +5170,7 @@
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>10236672</v>
+        <v>10231484</v>
       </c>
       <c r="B101" t="s">
         <v>144</v>
@@ -5178,15 +5178,15 @@
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102">
-        <v>10238737</v>
+        <v>10236617</v>
       </c>
       <c r="B102" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103">
-        <v>10242280</v>
+        <v>10236618</v>
       </c>
       <c r="B103" t="s">
         <v>140</v>
@@ -5194,23 +5194,23 @@
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104">
-        <v>10242291</v>
+        <v>10236662</v>
       </c>
       <c r="B104" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105">
-        <v>10242293</v>
+        <v>10236672</v>
       </c>
       <c r="B105" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106">
-        <v>10247603</v>
+        <v>10238737</v>
       </c>
       <c r="B106" t="s">
         <v>143</v>
@@ -5218,23 +5218,55 @@
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107">
-        <v>10247604</v>
+        <v>10242280</v>
       </c>
       <c r="B107" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108">
+        <v>10242291</v>
+      </c>
+      <c r="B108" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>10242293</v>
+      </c>
+      <c r="B109" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>10247603</v>
+      </c>
+      <c r="B110" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>10247604</v>
+      </c>
+      <c r="B111" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A112">
         <v>10247605</v>
       </c>
-      <c r="B108" t="s">
+      <c r="B112" t="s">
         <v>143</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:B108" xr:uid="{3EE41E71-179D-477A-9226-D4B51EEC218A}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B108">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B112">
       <sortCondition ref="A1:A108"/>
     </sortState>
   </autoFilter>
@@ -5324,11 +5356,11 @@
       </c>
       <c r="D4" s="16" t="str">
         <f>IF(Imprimir!B4="", "", _xlfn.XLOOKUP(VALUE(Imprimir!B4),DB!A:A,DB!B:B,""))</f>
-        <v/>
+        <v>BOX</v>
       </c>
       <c r="E4" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C2),"",'Colar Pedido'!D2)</f>
-        <v>0000011925</v>
+        <f>IF(ISBLANK('Colar Pedido'!C2),"",'Colar Pedido'!C2)</f>
+        <v>0000118134</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -5346,11 +5378,11 @@
       </c>
       <c r="D5" s="16" t="str">
         <f>IF(Imprimir!B5="", "", _xlfn.XLOOKUP(VALUE(Imprimir!B5),DB!A:A,DB!B:B,""))</f>
-        <v/>
+        <v>BOX</v>
       </c>
       <c r="E5" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C3),"",'Colar Pedido'!D3)</f>
-        <v>0000008709</v>
+        <f>IF(ISBLANK('Colar Pedido'!C3),"",'Colar Pedido'!C3)</f>
+        <v>0000118130</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -5371,8 +5403,8 @@
         <v>BOX</v>
       </c>
       <c r="E6" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C4),"",'Colar Pedido'!D4)</f>
-        <v>0000013709</v>
+        <f>IF(ISBLANK('Colar Pedido'!C4),"",'Colar Pedido'!C4)</f>
+        <v>0000118123</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -5393,8 +5425,8 @@
         <v>BOX</v>
       </c>
       <c r="E7" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C5),"",'Colar Pedido'!D5)</f>
-        <v>0000013830</v>
+        <f>IF(ISBLANK('Colar Pedido'!C5),"",'Colar Pedido'!C5)</f>
+        <v>0000118124</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -5415,8 +5447,8 @@
         <v>BOX</v>
       </c>
       <c r="E8" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C6),"",'Colar Pedido'!D6)</f>
-        <v>0000013563</v>
+        <f>IF(ISBLANK('Colar Pedido'!C6),"",'Colar Pedido'!C6)</f>
+        <v>0000118125</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -5437,8 +5469,8 @@
         <v>BOX</v>
       </c>
       <c r="E9" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C7),"",'Colar Pedido'!D7)</f>
-        <v>0000013019</v>
+        <f>IF(ISBLANK('Colar Pedido'!C7),"",'Colar Pedido'!C7)</f>
+        <v>0000118126</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -5459,8 +5491,8 @@
         <v>BOX</v>
       </c>
       <c r="E10" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C8),"",'Colar Pedido'!D8)</f>
-        <v>0000013833</v>
+        <f>IF(ISBLANK('Colar Pedido'!C8),"",'Colar Pedido'!C8)</f>
+        <v>0000118227</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -5481,8 +5513,8 @@
         <v>SLIVE</v>
       </c>
       <c r="E11" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C9),"",'Colar Pedido'!D9)</f>
-        <v>0000013886</v>
+        <f>IF(ISBLANK('Colar Pedido'!C9),"",'Colar Pedido'!C9)</f>
+        <v>0000118228</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -5503,8 +5535,8 @@
         <v>SLIVE</v>
       </c>
       <c r="E12" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C10),"",'Colar Pedido'!D10)</f>
-        <v>0000013876</v>
+        <f>IF(ISBLANK('Colar Pedido'!C10),"",'Colar Pedido'!C10)</f>
+        <v>0000118229</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -5525,8 +5557,8 @@
         <v>SLIVE</v>
       </c>
       <c r="E13" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C11),"",'Colar Pedido'!D11)</f>
-        <v>0000013835</v>
+        <f>IF(ISBLANK('Colar Pedido'!C11),"",'Colar Pedido'!C11)</f>
+        <v>0000118230</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -5547,8 +5579,8 @@
         <v>SLIVE</v>
       </c>
       <c r="E14" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C12),"",'Colar Pedido'!D12)</f>
-        <v>0000013853</v>
+        <f>IF(ISBLANK('Colar Pedido'!C12),"",'Colar Pedido'!C12)</f>
+        <v>0000118231</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -5569,8 +5601,8 @@
         <v>SLIVE</v>
       </c>
       <c r="E15" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C13),"",'Colar Pedido'!D13)</f>
-        <v>0000013834</v>
+        <f>IF(ISBLANK('Colar Pedido'!C13),"",'Colar Pedido'!C13)</f>
+        <v>0000118232</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -5591,8 +5623,8 @@
         <v>BOX</v>
       </c>
       <c r="E16" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C14),"",'Colar Pedido'!D14)</f>
-        <v>0000013495</v>
+        <f>IF(ISBLANK('Colar Pedido'!C14),"",'Colar Pedido'!C14)</f>
+        <v>0000118233</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -5613,8 +5645,8 @@
         <v>BOX</v>
       </c>
       <c r="E17" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C15),"",'Colar Pedido'!D15)</f>
-        <v>0000010158</v>
+        <f>IF(ISBLANK('Colar Pedido'!C15),"",'Colar Pedido'!C15)</f>
+        <v>0000118234</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -5635,8 +5667,8 @@
         <v>BOX</v>
       </c>
       <c r="E18" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C16),"",'Colar Pedido'!D16)</f>
-        <v>0000013562</v>
+        <f>IF(ISBLANK('Colar Pedido'!C16),"",'Colar Pedido'!C16)</f>
+        <v>0000118235</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -5657,8 +5689,8 @@
         <v>SLIVE</v>
       </c>
       <c r="E19" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C17),"",'Colar Pedido'!D17)</f>
-        <v>0000012489</v>
+        <f>IF(ISBLANK('Colar Pedido'!C17),"",'Colar Pedido'!C17)</f>
+        <v>0000118236</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -5679,8 +5711,8 @@
         <v>BOX</v>
       </c>
       <c r="E20" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C18),"",'Colar Pedido'!D18)</f>
-        <v>0000013896</v>
+        <f>IF(ISBLANK('Colar Pedido'!C18),"",'Colar Pedido'!C18)</f>
+        <v>0000118237</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -5701,8 +5733,8 @@
         <v>SLIVE</v>
       </c>
       <c r="E21" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C19),"",'Colar Pedido'!D19)</f>
-        <v>0000014043</v>
+        <f>IF(ISBLANK('Colar Pedido'!C19),"",'Colar Pedido'!C19)</f>
+        <v>0000118238</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -5723,8 +5755,8 @@
         <v>SLIVE</v>
       </c>
       <c r="E22" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C20),"",'Colar Pedido'!D20)</f>
-        <v>0000014043</v>
+        <f>IF(ISBLANK('Colar Pedido'!C20),"",'Colar Pedido'!C20)</f>
+        <v>0000118239</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -5745,8 +5777,8 @@
         <v>SLIVE</v>
       </c>
       <c r="E23" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C21),"",'Colar Pedido'!D21)</f>
-        <v>0000014066</v>
+        <f>IF(ISBLANK('Colar Pedido'!C21),"",'Colar Pedido'!C21)</f>
+        <v>0000118240</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -5767,8 +5799,8 @@
         <v>BOX</v>
       </c>
       <c r="E24" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C22),"",'Colar Pedido'!D22)</f>
-        <v>0000011465</v>
+        <f>IF(ISBLANK('Colar Pedido'!C22),"",'Colar Pedido'!C22)</f>
+        <v>0000118241</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -5789,8 +5821,8 @@
         <v>BOX</v>
       </c>
       <c r="E25" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C23),"",'Colar Pedido'!D23)</f>
-        <v>0000013467</v>
+        <f>IF(ISBLANK('Colar Pedido'!C23),"",'Colar Pedido'!C23)</f>
+        <v>0000118242</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -5811,8 +5843,8 @@
         <v>BOX</v>
       </c>
       <c r="E26" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C24),"",'Colar Pedido'!D24)</f>
-        <v>0000009496</v>
+        <f>IF(ISBLANK('Colar Pedido'!C24),"",'Colar Pedido'!C24)</f>
+        <v>0000118243</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -5833,8 +5865,8 @@
         <v/>
       </c>
       <c r="E27" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C25),"",'Colar Pedido'!D25)</f>
-        <v>0000013869</v>
+        <f>IF(ISBLANK('Colar Pedido'!C25),"",'Colar Pedido'!C25)</f>
+        <v>0000118244</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -5855,8 +5887,8 @@
         <v>SLIVE</v>
       </c>
       <c r="E28" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C26),"",'Colar Pedido'!D26)</f>
-        <v>0000014064</v>
+        <f>IF(ISBLANK('Colar Pedido'!C26),"",'Colar Pedido'!C26)</f>
+        <v>0000118245</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -5874,11 +5906,11 @@
       </c>
       <c r="D29" s="16" t="str">
         <f>IF(Imprimir!B29="", "", _xlfn.XLOOKUP(VALUE(Imprimir!B29),DB!A:A,DB!B:B,""))</f>
-        <v/>
+        <v>SLEEVE P</v>
       </c>
       <c r="E29" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C27),"",'Colar Pedido'!D27)</f>
-        <v>0000013843</v>
+        <f>IF(ISBLANK('Colar Pedido'!C27),"",'Colar Pedido'!C27)</f>
+        <v>0000118246</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -5896,11 +5928,11 @@
       </c>
       <c r="D30" s="16" t="str">
         <f>IF(Imprimir!B30="", "", _xlfn.XLOOKUP(VALUE(Imprimir!B30),DB!A:A,DB!B:B,""))</f>
-        <v/>
+        <v>SLEEVE P</v>
       </c>
       <c r="E30" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C28),"",'Colar Pedido'!D28)</f>
-        <v>0000013859</v>
+        <f>IF(ISBLANK('Colar Pedido'!C28),"",'Colar Pedido'!C28)</f>
+        <v>0000118247</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -5918,11 +5950,11 @@
       </c>
       <c r="D31" s="16" t="str">
         <f>IF(Imprimir!B31="", "", _xlfn.XLOOKUP(VALUE(Imprimir!B31),DB!A:A,DB!B:B,""))</f>
-        <v/>
+        <v>SLEEVE P</v>
       </c>
       <c r="E31" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C29),"",'Colar Pedido'!D29)</f>
-        <v>0000013841</v>
+        <f>IF(ISBLANK('Colar Pedido'!C29),"",'Colar Pedido'!C29)</f>
+        <v>0000118248</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -5943,8 +5975,8 @@
         <v>SLIVE</v>
       </c>
       <c r="E32" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C30),"",'Colar Pedido'!D30)</f>
-        <v>0000013851</v>
+        <f>IF(ISBLANK('Colar Pedido'!C30),"",'Colar Pedido'!C30)</f>
+        <v>0000118249</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -5962,11 +5994,11 @@
       </c>
       <c r="D33" s="16" t="str">
         <f>IF(Imprimir!B33="", "", _xlfn.XLOOKUP(VALUE(Imprimir!B33),DB!A:A,DB!B:B,""))</f>
-        <v/>
+        <v>BOX</v>
       </c>
       <c r="E33" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C31),"",'Colar Pedido'!D31)</f>
-        <v>0000013863</v>
+        <f>IF(ISBLANK('Colar Pedido'!C31),"",'Colar Pedido'!C31)</f>
+        <v>0000118250</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -5984,11 +6016,11 @@
       </c>
       <c r="D34" s="16" t="str">
         <f>IF(Imprimir!B34="", "", _xlfn.XLOOKUP(VALUE(Imprimir!B34),DB!A:A,DB!B:B,""))</f>
-        <v/>
+        <v>BOX</v>
       </c>
       <c r="E34" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C32),"",'Colar Pedido'!D32)</f>
-        <v>0000013870</v>
+        <f>IF(ISBLANK('Colar Pedido'!C32),"",'Colar Pedido'!C32)</f>
+        <v>0000118251</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -6006,11 +6038,11 @@
       </c>
       <c r="D35" s="16" t="str">
         <f>IF(Imprimir!B35="", "", _xlfn.XLOOKUP(VALUE(Imprimir!B35),DB!A:A,DB!B:B,""))</f>
-        <v/>
+        <v>BOX</v>
       </c>
       <c r="E35" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C33),"",'Colar Pedido'!D33)</f>
-        <v>0000013883</v>
+        <f>IF(ISBLANK('Colar Pedido'!C33),"",'Colar Pedido'!C33)</f>
+        <v>0000118252</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -6028,11 +6060,11 @@
       </c>
       <c r="D36" s="16" t="str">
         <f>IF(Imprimir!B36="", "", _xlfn.XLOOKUP(VALUE(Imprimir!B36),DB!A:A,DB!B:B,""))</f>
-        <v/>
+        <v>BOX</v>
       </c>
       <c r="E36" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C34),"",'Colar Pedido'!D34)</f>
-        <v>0000013706</v>
+        <f>IF(ISBLANK('Colar Pedido'!C34),"",'Colar Pedido'!C34)</f>
+        <v>0000118253</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -6053,8 +6085,8 @@
         <v>BOX</v>
       </c>
       <c r="E37" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C35),"",'Colar Pedido'!D35)</f>
-        <v>0000013837</v>
+        <f>IF(ISBLANK('Colar Pedido'!C35),"",'Colar Pedido'!C35)</f>
+        <v>0000118254</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -6075,8 +6107,8 @@
         <v>BOX</v>
       </c>
       <c r="E38" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C36),"",'Colar Pedido'!D36)</f>
-        <v>0000011775</v>
+        <f>IF(ISBLANK('Colar Pedido'!C36),"",'Colar Pedido'!C36)</f>
+        <v>0000118255</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -6097,8 +6129,8 @@
         <v>BOX</v>
       </c>
       <c r="E39" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C37),"",'Colar Pedido'!D37)</f>
-        <v>0000013840</v>
+        <f>IF(ISBLANK('Colar Pedido'!C37),"",'Colar Pedido'!C37)</f>
+        <v>0000118256</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -6119,8 +6151,8 @@
         <v>SLIVE</v>
       </c>
       <c r="E40" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C38),"",'Colar Pedido'!D38)</f>
-        <v>0000013728</v>
+        <f>IF(ISBLANK('Colar Pedido'!C38),"",'Colar Pedido'!C38)</f>
+        <v>0000118257</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -6141,8 +6173,8 @@
         <v>SLEEVE P</v>
       </c>
       <c r="E41" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C39),"",'Colar Pedido'!D39)</f>
-        <v>0000013735</v>
+        <f>IF(ISBLANK('Colar Pedido'!C39),"",'Colar Pedido'!C39)</f>
+        <v>0000118258</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -6163,8 +6195,8 @@
         <v>NINE</v>
       </c>
       <c r="E42" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C40),"",'Colar Pedido'!D40)</f>
-        <v>0000013438</v>
+        <f>IF(ISBLANK('Colar Pedido'!C40),"",'Colar Pedido'!C40)</f>
+        <v>0000118259</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -6185,8 +6217,8 @@
         <v>NINE</v>
       </c>
       <c r="E43" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C41),"",'Colar Pedido'!D41)</f>
-        <v>0000013942</v>
+        <f>IF(ISBLANK('Colar Pedido'!C41),"",'Colar Pedido'!C41)</f>
+        <v>0000118260</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -6207,8 +6239,8 @@
         <v>BOX</v>
       </c>
       <c r="E44" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C42),"",'Colar Pedido'!D42)</f>
-        <v>0000013436</v>
+        <f>IF(ISBLANK('Colar Pedido'!C42),"",'Colar Pedido'!C42)</f>
+        <v>0000118261</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
@@ -6229,8 +6261,8 @@
         <v>BOX</v>
       </c>
       <c r="E45" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C43),"",'Colar Pedido'!D43)</f>
-        <v>0000012543</v>
+        <f>IF(ISBLANK('Colar Pedido'!C43),"",'Colar Pedido'!C43)</f>
+        <v>0000118262</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
@@ -6251,8 +6283,8 @@
         <v>BOX</v>
       </c>
       <c r="E46" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C44),"",'Colar Pedido'!D44)</f>
-        <v>0000012647</v>
+        <f>IF(ISBLANK('Colar Pedido'!C44),"",'Colar Pedido'!C44)</f>
+        <v>0000118263</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -6270,11 +6302,11 @@
       </c>
       <c r="D47" s="16" t="str">
         <f>IF(Imprimir!B47="", "", _xlfn.XLOOKUP(VALUE(Imprimir!B47),DB!A:A,DB!B:B,""))</f>
-        <v/>
+        <v>BOX</v>
       </c>
       <c r="E47" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C45),"",'Colar Pedido'!D45)</f>
-        <v>0000013912</v>
+        <f>IF(ISBLANK('Colar Pedido'!C45),"",'Colar Pedido'!C45)</f>
+        <v>0000118264</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -6295,8 +6327,8 @@
         <v/>
       </c>
       <c r="E48" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C46),"",'Colar Pedido'!D46)</f>
-        <v>0000013088</v>
+        <f>IF(ISBLANK('Colar Pedido'!C46),"",'Colar Pedido'!C46)</f>
+        <v>0000118265</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -6317,8 +6349,8 @@
         <v/>
       </c>
       <c r="E49" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C47),"",'Colar Pedido'!D47)</f>
-        <v>0000013088</v>
+        <f>IF(ISBLANK('Colar Pedido'!C47),"",'Colar Pedido'!C47)</f>
+        <v>0000118266</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -6336,11 +6368,11 @@
       </c>
       <c r="D50" s="16" t="str">
         <f>IF(Imprimir!B50="", "", _xlfn.XLOOKUP(VALUE(Imprimir!B50),DB!A:A,DB!B:B,""))</f>
-        <v/>
+        <v>BOX</v>
       </c>
       <c r="E50" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C48),"",'Colar Pedido'!D48)</f>
-        <v>0000013864</v>
+        <f>IF(ISBLANK('Colar Pedido'!C48),"",'Colar Pedido'!C48)</f>
+        <v>0000118267</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -6361,7 +6393,7 @@
         <v/>
       </c>
       <c r="E51" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C49),"",'Colar Pedido'!D49)</f>
+        <f>IF(ISBLANK('Colar Pedido'!C49),"",'Colar Pedido'!C49)</f>
         <v/>
       </c>
     </row>
@@ -6383,7 +6415,7 @@
         <v/>
       </c>
       <c r="E52" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C50),"",'Colar Pedido'!D50)</f>
+        <f>IF(ISBLANK('Colar Pedido'!C50),"",'Colar Pedido'!C50)</f>
         <v/>
       </c>
     </row>
@@ -6405,7 +6437,7 @@
         <v/>
       </c>
       <c r="E53" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C51),"",'Colar Pedido'!D51)</f>
+        <f>IF(ISBLANK('Colar Pedido'!C51),"",'Colar Pedido'!C51)</f>
         <v/>
       </c>
     </row>
@@ -6427,7 +6459,7 @@
         <v/>
       </c>
       <c r="E54" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C52),"",'Colar Pedido'!D52)</f>
+        <f>IF(ISBLANK('Colar Pedido'!C52),"",'Colar Pedido'!C52)</f>
         <v/>
       </c>
     </row>
@@ -6449,7 +6481,7 @@
         <v/>
       </c>
       <c r="E55" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C53),"",'Colar Pedido'!D53)</f>
+        <f>IF(ISBLANK('Colar Pedido'!C53),"",'Colar Pedido'!C53)</f>
         <v/>
       </c>
     </row>
@@ -6471,7 +6503,7 @@
         <v/>
       </c>
       <c r="E56" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C54),"",'Colar Pedido'!D54)</f>
+        <f>IF(ISBLANK('Colar Pedido'!C54),"",'Colar Pedido'!C54)</f>
         <v/>
       </c>
     </row>
@@ -6493,7 +6525,7 @@
         <v/>
       </c>
       <c r="E57" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C55),"",'Colar Pedido'!D55)</f>
+        <f>IF(ISBLANK('Colar Pedido'!C55),"",'Colar Pedido'!C55)</f>
         <v/>
       </c>
     </row>
@@ -6515,7 +6547,7 @@
         <v/>
       </c>
       <c r="E58" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C56),"",'Colar Pedido'!D56)</f>
+        <f>IF(ISBLANK('Colar Pedido'!C56),"",'Colar Pedido'!C56)</f>
         <v/>
       </c>
     </row>
@@ -6537,7 +6569,7 @@
         <v/>
       </c>
       <c r="E59" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C57),"",'Colar Pedido'!D57)</f>
+        <f>IF(ISBLANK('Colar Pedido'!C57),"",'Colar Pedido'!C57)</f>
         <v/>
       </c>
     </row>
@@ -6559,7 +6591,7 @@
         <v/>
       </c>
       <c r="E60" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C58),"",'Colar Pedido'!D58)</f>
+        <f>IF(ISBLANK('Colar Pedido'!C58),"",'Colar Pedido'!C58)</f>
         <v/>
       </c>
     </row>
@@ -6581,7 +6613,7 @@
         <v/>
       </c>
       <c r="E61" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C59),"",'Colar Pedido'!D59)</f>
+        <f>IF(ISBLANK('Colar Pedido'!C59),"",'Colar Pedido'!C59)</f>
         <v/>
       </c>
     </row>
@@ -6603,7 +6635,7 @@
         <v/>
       </c>
       <c r="E62" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C60),"",'Colar Pedido'!D60)</f>
+        <f>IF(ISBLANK('Colar Pedido'!C60),"",'Colar Pedido'!C60)</f>
         <v/>
       </c>
     </row>
@@ -6625,7 +6657,7 @@
         <v/>
       </c>
       <c r="E63" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C61),"",'Colar Pedido'!D61)</f>
+        <f>IF(ISBLANK('Colar Pedido'!C61),"",'Colar Pedido'!C61)</f>
         <v/>
       </c>
     </row>
@@ -6647,7 +6679,7 @@
         <v/>
       </c>
       <c r="E64" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C62),"",'Colar Pedido'!D62)</f>
+        <f>IF(ISBLANK('Colar Pedido'!C62),"",'Colar Pedido'!C62)</f>
         <v/>
       </c>
     </row>
@@ -6669,7 +6701,7 @@
         <v/>
       </c>
       <c r="E65" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C63),"",'Colar Pedido'!D63)</f>
+        <f>IF(ISBLANK('Colar Pedido'!C63),"",'Colar Pedido'!C63)</f>
         <v/>
       </c>
     </row>
@@ -6691,7 +6723,7 @@
         <v/>
       </c>
       <c r="E66" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C64),"",'Colar Pedido'!D64)</f>
+        <f>IF(ISBLANK('Colar Pedido'!C64),"",'Colar Pedido'!C64)</f>
         <v/>
       </c>
     </row>
@@ -6713,7 +6745,7 @@
         <v/>
       </c>
       <c r="E67" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C65),"",'Colar Pedido'!D65)</f>
+        <f>IF(ISBLANK('Colar Pedido'!C65),"",'Colar Pedido'!C65)</f>
         <v/>
       </c>
     </row>
@@ -6735,7 +6767,7 @@
         <v/>
       </c>
       <c r="E68" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C66),"",'Colar Pedido'!D66)</f>
+        <f>IF(ISBLANK('Colar Pedido'!C66),"",'Colar Pedido'!C66)</f>
         <v/>
       </c>
     </row>
@@ -6757,7 +6789,7 @@
         <v/>
       </c>
       <c r="E69" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C67),"",'Colar Pedido'!D67)</f>
+        <f>IF(ISBLANK('Colar Pedido'!C67),"",'Colar Pedido'!C67)</f>
         <v/>
       </c>
     </row>
@@ -6779,7 +6811,7 @@
         <v/>
       </c>
       <c r="E70" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C68),"",'Colar Pedido'!D68)</f>
+        <f>IF(ISBLANK('Colar Pedido'!C68),"",'Colar Pedido'!C68)</f>
         <v/>
       </c>
     </row>
@@ -6801,7 +6833,7 @@
         <v/>
       </c>
       <c r="E71" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C69),"",'Colar Pedido'!D69)</f>
+        <f>IF(ISBLANK('Colar Pedido'!C69),"",'Colar Pedido'!C69)</f>
         <v/>
       </c>
     </row>
@@ -6823,7 +6855,7 @@
         <v/>
       </c>
       <c r="E72" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C70),"",'Colar Pedido'!D70)</f>
+        <f>IF(ISBLANK('Colar Pedido'!C70),"",'Colar Pedido'!C70)</f>
         <v/>
       </c>
     </row>
@@ -6845,7 +6877,7 @@
         <v/>
       </c>
       <c r="E73" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C71),"",'Colar Pedido'!D71)</f>
+        <f>IF(ISBLANK('Colar Pedido'!C71),"",'Colar Pedido'!C71)</f>
         <v/>
       </c>
     </row>
@@ -6867,7 +6899,7 @@
         <v/>
       </c>
       <c r="E74" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C72),"",'Colar Pedido'!D72)</f>
+        <f>IF(ISBLANK('Colar Pedido'!C72),"",'Colar Pedido'!C72)</f>
         <v/>
       </c>
     </row>
@@ -6889,7 +6921,7 @@
         <v/>
       </c>
       <c r="E75" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C73),"",'Colar Pedido'!D73)</f>
+        <f>IF(ISBLANK('Colar Pedido'!C73),"",'Colar Pedido'!C73)</f>
         <v/>
       </c>
     </row>
@@ -6911,7 +6943,7 @@
         <v/>
       </c>
       <c r="E76" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C74),"",'Colar Pedido'!D74)</f>
+        <f>IF(ISBLANK('Colar Pedido'!C74),"",'Colar Pedido'!C74)</f>
         <v/>
       </c>
     </row>
@@ -6933,7 +6965,7 @@
         <v/>
       </c>
       <c r="E77" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C75),"",'Colar Pedido'!D75)</f>
+        <f>IF(ISBLANK('Colar Pedido'!C75),"",'Colar Pedido'!C75)</f>
         <v/>
       </c>
     </row>
@@ -6955,7 +6987,7 @@
         <v/>
       </c>
       <c r="E78" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C76),"",'Colar Pedido'!D76)</f>
+        <f>IF(ISBLANK('Colar Pedido'!C76),"",'Colar Pedido'!C76)</f>
         <v/>
       </c>
     </row>
@@ -6977,7 +7009,7 @@
         <v/>
       </c>
       <c r="E79" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C77),"",'Colar Pedido'!D77)</f>
+        <f>IF(ISBLANK('Colar Pedido'!C77),"",'Colar Pedido'!C77)</f>
         <v/>
       </c>
     </row>
@@ -6999,7 +7031,7 @@
         <v/>
       </c>
       <c r="E80" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C78),"",'Colar Pedido'!D78)</f>
+        <f>IF(ISBLANK('Colar Pedido'!C78),"",'Colar Pedido'!C78)</f>
         <v/>
       </c>
     </row>
@@ -7021,7 +7053,7 @@
         <v/>
       </c>
       <c r="E81" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C79),"",'Colar Pedido'!D79)</f>
+        <f>IF(ISBLANK('Colar Pedido'!C79),"",'Colar Pedido'!C79)</f>
         <v/>
       </c>
     </row>
@@ -7043,7 +7075,7 @@
         <v/>
       </c>
       <c r="E82" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C80),"",'Colar Pedido'!D80)</f>
+        <f>IF(ISBLANK('Colar Pedido'!C80),"",'Colar Pedido'!C80)</f>
         <v/>
       </c>
     </row>
@@ -7065,7 +7097,7 @@
         <v/>
       </c>
       <c r="E83" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C81),"",'Colar Pedido'!D81)</f>
+        <f>IF(ISBLANK('Colar Pedido'!C81),"",'Colar Pedido'!C81)</f>
         <v/>
       </c>
     </row>
@@ -7087,7 +7119,7 @@
         <v/>
       </c>
       <c r="E84" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C82),"",'Colar Pedido'!D82)</f>
+        <f>IF(ISBLANK('Colar Pedido'!C82),"",'Colar Pedido'!C82)</f>
         <v/>
       </c>
     </row>
@@ -7109,7 +7141,7 @@
         <v/>
       </c>
       <c r="E85" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C83),"",'Colar Pedido'!D83)</f>
+        <f>IF(ISBLANK('Colar Pedido'!C83),"",'Colar Pedido'!C83)</f>
         <v/>
       </c>
     </row>
@@ -7131,7 +7163,7 @@
         <v/>
       </c>
       <c r="E86" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C84),"",'Colar Pedido'!D84)</f>
+        <f>IF(ISBLANK('Colar Pedido'!C84),"",'Colar Pedido'!C84)</f>
         <v/>
       </c>
     </row>
@@ -7153,7 +7185,7 @@
         <v/>
       </c>
       <c r="E87" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C85),"",'Colar Pedido'!D85)</f>
+        <f>IF(ISBLANK('Colar Pedido'!C85),"",'Colar Pedido'!C85)</f>
         <v/>
       </c>
     </row>
@@ -7175,7 +7207,7 @@
         <v/>
       </c>
       <c r="E88" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C86),"",'Colar Pedido'!D86)</f>
+        <f>IF(ISBLANK('Colar Pedido'!C86),"",'Colar Pedido'!C86)</f>
         <v/>
       </c>
     </row>
@@ -7197,7 +7229,7 @@
         <v/>
       </c>
       <c r="E89" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C87),"",'Colar Pedido'!D87)</f>
+        <f>IF(ISBLANK('Colar Pedido'!C87),"",'Colar Pedido'!C87)</f>
         <v/>
       </c>
     </row>
@@ -7219,7 +7251,7 @@
         <v/>
       </c>
       <c r="E90" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C88),"",'Colar Pedido'!D88)</f>
+        <f>IF(ISBLANK('Colar Pedido'!C88),"",'Colar Pedido'!C88)</f>
         <v/>
       </c>
     </row>
@@ -7241,7 +7273,7 @@
         <v/>
       </c>
       <c r="E91" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C89),"",'Colar Pedido'!D89)</f>
+        <f>IF(ISBLANK('Colar Pedido'!C89),"",'Colar Pedido'!C89)</f>
         <v/>
       </c>
     </row>
@@ -7263,7 +7295,7 @@
         <v/>
       </c>
       <c r="E92" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C90),"",'Colar Pedido'!D90)</f>
+        <f>IF(ISBLANK('Colar Pedido'!C90),"",'Colar Pedido'!C90)</f>
         <v/>
       </c>
     </row>
@@ -7285,7 +7317,7 @@
         <v/>
       </c>
       <c r="E93" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C91),"",'Colar Pedido'!D91)</f>
+        <f>IF(ISBLANK('Colar Pedido'!C91),"",'Colar Pedido'!C91)</f>
         <v/>
       </c>
     </row>
@@ -7307,7 +7339,7 @@
         <v/>
       </c>
       <c r="E94" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C92),"",'Colar Pedido'!D92)</f>
+        <f>IF(ISBLANK('Colar Pedido'!C92),"",'Colar Pedido'!C92)</f>
         <v/>
       </c>
     </row>
@@ -7329,7 +7361,7 @@
         <v/>
       </c>
       <c r="E95" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C93),"",'Colar Pedido'!D93)</f>
+        <f>IF(ISBLANK('Colar Pedido'!C93),"",'Colar Pedido'!C93)</f>
         <v/>
       </c>
     </row>
@@ -7351,7 +7383,7 @@
         <v/>
       </c>
       <c r="E96" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C94),"",'Colar Pedido'!D94)</f>
+        <f>IF(ISBLANK('Colar Pedido'!C94),"",'Colar Pedido'!C94)</f>
         <v/>
       </c>
     </row>
@@ -7373,7 +7405,7 @@
         <v/>
       </c>
       <c r="E97" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C95),"",'Colar Pedido'!D95)</f>
+        <f>IF(ISBLANK('Colar Pedido'!C95),"",'Colar Pedido'!C95)</f>
         <v/>
       </c>
     </row>
@@ -7395,7 +7427,7 @@
         <v/>
       </c>
       <c r="E98" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C96),"",'Colar Pedido'!D96)</f>
+        <f>IF(ISBLANK('Colar Pedido'!C96),"",'Colar Pedido'!C96)</f>
         <v/>
       </c>
     </row>
@@ -7417,7 +7449,7 @@
         <v/>
       </c>
       <c r="E99" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C97),"",'Colar Pedido'!D97)</f>
+        <f>IF(ISBLANK('Colar Pedido'!C97),"",'Colar Pedido'!C97)</f>
         <v/>
       </c>
     </row>
@@ -7439,7 +7471,7 @@
         <v/>
       </c>
       <c r="E100" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C98),"",'Colar Pedido'!D98)</f>
+        <f>IF(ISBLANK('Colar Pedido'!C98),"",'Colar Pedido'!C98)</f>
         <v/>
       </c>
     </row>
@@ -7461,7 +7493,7 @@
         <v/>
       </c>
       <c r="E101" s="16" t="str">
-        <f>IF(ISBLANK('Colar Pedido'!C99),"",'Colar Pedido'!D99)</f>
+        <f>IF(ISBLANK('Colar Pedido'!C99),"",'Colar Pedido'!C99)</f>
         <v/>
       </c>
     </row>

--- a/Picking by Case ID.xlsx
+++ b/Picking by Case ID.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dsvcorp-my.sharepoint.com/personal/wendel_santos1_dsv_com/Documents/Documents/code/case-id-barcode-generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="62" documentId="8_{33C33F29-AEF1-4D5A-A65C-4D1749FCB150}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22CC86CE-6DA2-4360-BBAB-1533359C8CF5}"/>
+  <xr:revisionPtr revIDLastSave="66" documentId="8_{33C33F29-AEF1-4D5A-A65C-4D1749FCB150}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B92BD0C-D180-4B6B-B1DF-A4970A754053}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="828" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="713" uniqueCount="230">
   <si>
     <t>Order Number</t>
   </si>
@@ -89,12 +89,6 @@
     <t>BRARQBAT02</t>
   </si>
   <si>
-    <t>10215641</t>
-  </si>
-  <si>
-    <t>200.00000</t>
-  </si>
-  <si>
     <t>Released</t>
   </si>
   <si>
@@ -116,342 +110,45 @@
     <t>00003</t>
   </si>
   <si>
-    <t>0000013833</t>
-  </si>
-  <si>
-    <t>BLH077</t>
-  </si>
-  <si>
-    <t>REC3259927753089ARQ</t>
-  </si>
-  <si>
-    <t>10223435</t>
-  </si>
-  <si>
-    <t>120.00000</t>
-  </si>
-  <si>
     <t>00004</t>
   </si>
   <si>
-    <t>0000013876</t>
-  </si>
-  <si>
-    <t>10223108</t>
-  </si>
-  <si>
-    <t>0000013835</t>
-  </si>
-  <si>
-    <t>BLG003</t>
-  </si>
-  <si>
-    <t>REC1490871577023ARQ</t>
-  </si>
-  <si>
     <t>00005</t>
   </si>
   <si>
-    <t>0000013853</t>
-  </si>
-  <si>
-    <t>BLE006</t>
-  </si>
-  <si>
-    <t>REC3259927753097ARQ</t>
-  </si>
-  <si>
-    <t>10226385</t>
-  </si>
-  <si>
     <t>20.00000</t>
   </si>
   <si>
     <t>00006</t>
   </si>
   <si>
-    <t>0000013834</t>
-  </si>
-  <si>
-    <t>BLF043</t>
-  </si>
-  <si>
-    <t>REC1490871577024ARQ</t>
-  </si>
-  <si>
-    <t>10226361</t>
-  </si>
-  <si>
     <t>00007</t>
   </si>
   <si>
-    <t>0000013495</t>
-  </si>
-  <si>
-    <t>BLF083</t>
-  </si>
-  <si>
-    <t>REC1DPULP81688ARQ</t>
-  </si>
-  <si>
-    <t>10224293</t>
-  </si>
-  <si>
     <t>40.00000</t>
   </si>
   <si>
     <t>00008</t>
   </si>
   <si>
-    <t>0000013562</t>
-  </si>
-  <si>
-    <t>BLH065</t>
-  </si>
-  <si>
-    <t>REC1DPULP81705ARQ</t>
-  </si>
-  <si>
-    <t>10223657</t>
-  </si>
-  <si>
     <t>00009</t>
   </si>
   <si>
-    <t>10198819</t>
-  </si>
-  <si>
-    <t>10.00000</t>
-  </si>
-  <si>
-    <t>0000012489</t>
-  </si>
-  <si>
-    <t>BLF037</t>
-  </si>
-  <si>
-    <t>REC125366K1278ARQ</t>
-  </si>
-  <si>
     <t>30.00000</t>
   </si>
   <si>
     <t>00010</t>
   </si>
   <si>
-    <t>00011</t>
-  </si>
-  <si>
-    <t>00012</t>
-  </si>
-  <si>
-    <t>00013</t>
-  </si>
-  <si>
-    <t>0000013896</t>
-  </si>
-  <si>
-    <t>BLD070</t>
-  </si>
-  <si>
-    <t>REC125366K1150ARQ</t>
-  </si>
-  <si>
-    <t>10226359</t>
-  </si>
-  <si>
-    <t>00014</t>
-  </si>
-  <si>
-    <t>BLF066</t>
-  </si>
-  <si>
-    <t>10226417</t>
-  </si>
-  <si>
-    <t>00015</t>
-  </si>
-  <si>
-    <t>00016</t>
-  </si>
-  <si>
-    <t>60.00000</t>
-  </si>
-  <si>
-    <t>00017</t>
-  </si>
-  <si>
-    <t>10226454</t>
-  </si>
-  <si>
-    <t>0000011465</t>
-  </si>
-  <si>
-    <t>BLG085</t>
-  </si>
-  <si>
-    <t>REC52C8I1395ARQ</t>
-  </si>
-  <si>
-    <t>00018</t>
-  </si>
-  <si>
-    <t>80.00000</t>
-  </si>
-  <si>
-    <t>00019</t>
-  </si>
-  <si>
-    <t>0000009496</t>
-  </si>
-  <si>
-    <t>BLD088</t>
-  </si>
-  <si>
-    <t>RECYTF1VD618ARQ</t>
-  </si>
-  <si>
-    <t>10227896</t>
-  </si>
-  <si>
-    <t>00020</t>
-  </si>
-  <si>
-    <t>0000013869</t>
-  </si>
-  <si>
-    <t>10226377</t>
-  </si>
-  <si>
-    <t>00021</t>
-  </si>
-  <si>
-    <t>0000014064</t>
-  </si>
-  <si>
-    <t>BLF076</t>
-  </si>
-  <si>
-    <t>REC16442122ARQ</t>
-  </si>
-  <si>
-    <t>10226403</t>
-  </si>
-  <si>
-    <t>00022</t>
-  </si>
-  <si>
-    <t>0000013859</t>
-  </si>
-  <si>
-    <t>BLE015</t>
-  </si>
-  <si>
-    <t>REC3259927753112ARQ</t>
-  </si>
-  <si>
-    <t>10226452</t>
-  </si>
-  <si>
-    <t>00023</t>
-  </si>
-  <si>
-    <t>00024</t>
-  </si>
-  <si>
-    <t>10226380</t>
-  </si>
-  <si>
-    <t>0000013863</t>
-  </si>
-  <si>
-    <t>BLG009</t>
-  </si>
-  <si>
-    <t>00025</t>
-  </si>
-  <si>
-    <t>10208005</t>
-  </si>
-  <si>
-    <t>00026</t>
-  </si>
-  <si>
-    <t>10226463</t>
-  </si>
-  <si>
     <t>110.00000</t>
   </si>
   <si>
-    <t>0000013728</t>
-  </si>
-  <si>
     <t>50.00000</t>
   </si>
   <si>
-    <t>00027</t>
-  </si>
-  <si>
-    <t>0000013735</t>
-  </si>
-  <si>
-    <t>BLH074</t>
-  </si>
-  <si>
-    <t>REC3259927753092ARQ</t>
-  </si>
-  <si>
-    <t>10208167</t>
-  </si>
-  <si>
-    <t>0000013438</t>
-  </si>
-  <si>
-    <t>BLE031</t>
-  </si>
-  <si>
-    <t>REC1DPULOU934ARQ</t>
-  </si>
-  <si>
     <t>10226367</t>
   </si>
   <si>
-    <t>10226386</t>
-  </si>
-  <si>
-    <t>0000013864</t>
-  </si>
-  <si>
-    <t>BLE005</t>
-  </si>
-  <si>
-    <t>REC3259927753119ARQ</t>
-  </si>
-  <si>
-    <t>10242293</t>
-  </si>
-  <si>
-    <t>70.00000</t>
-  </si>
-  <si>
-    <t>10226404</t>
-  </si>
-  <si>
-    <t>0000013912</t>
-  </si>
-  <si>
-    <t>BLF001</t>
-  </si>
-  <si>
-    <t>RECF05QS7402ARQ</t>
-  </si>
-  <si>
-    <t>170.00000</t>
-  </si>
-  <si>
-    <t>BLF002</t>
-  </si>
-  <si>
     <t>10226461</t>
   </si>
   <si>
@@ -557,348 +254,18 @@
     <t>Passo Fundo</t>
   </si>
   <si>
-    <t>Abrir</t>
-  </si>
-  <si>
     <t>Itajaí</t>
   </si>
   <si>
-    <t>6878107316</t>
-  </si>
-  <si>
-    <t>0000118134</t>
-  </si>
-  <si>
-    <t>0000011925</t>
-  </si>
-  <si>
-    <t>FR.01.02.01.04</t>
-  </si>
-  <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>0000001887</t>
-  </si>
-  <si>
-    <t>0000118130</t>
-  </si>
-  <si>
-    <t>0000008709</t>
-  </si>
-  <si>
-    <t>FR.01.02.01.03</t>
-  </si>
-  <si>
-    <t>0000118123</t>
-  </si>
-  <si>
-    <t>0000013709</t>
-  </si>
-  <si>
-    <t>BLH057</t>
-  </si>
-  <si>
-    <t>REC3259927753091ARQ</t>
-  </si>
-  <si>
-    <t>0000118124</t>
-  </si>
-  <si>
-    <t>0000013830</t>
-  </si>
-  <si>
-    <t>REC3259927753086ARQ</t>
-  </si>
-  <si>
-    <t>0000118125</t>
-  </si>
-  <si>
-    <t>0000013563</t>
-  </si>
-  <si>
-    <t>BLH079</t>
-  </si>
-  <si>
-    <t>REC1DPULP81683ARQ</t>
-  </si>
-  <si>
-    <t>0000118126</t>
-  </si>
-  <si>
-    <t>0000013019</t>
-  </si>
-  <si>
-    <t>BLG087</t>
-  </si>
-  <si>
-    <t>REC1DPULP71553ARQ</t>
-  </si>
-  <si>
-    <t>0000118227</t>
-  </si>
-  <si>
-    <t>0000118228</t>
-  </si>
-  <si>
-    <t>0000013886</t>
-  </si>
-  <si>
-    <t>REC1490871577026ARQ</t>
-  </si>
-  <si>
-    <t>0000118229</t>
-  </si>
-  <si>
-    <t>BLH058</t>
-  </si>
-  <si>
-    <t>REC52C8ID604ARQ</t>
-  </si>
-  <si>
-    <t>0000118230</t>
-  </si>
-  <si>
-    <t>0000118231</t>
-  </si>
-  <si>
-    <t>0000118232</t>
-  </si>
-  <si>
-    <t>0000118233</t>
-  </si>
-  <si>
-    <t>0000118234</t>
-  </si>
-  <si>
-    <t>0000010158</t>
-  </si>
-  <si>
-    <t>BLF089</t>
-  </si>
-  <si>
-    <t>REC1733RLE207ARQ</t>
-  </si>
-  <si>
-    <t>0000118235</t>
-  </si>
-  <si>
-    <t>0000118236</t>
-  </si>
-  <si>
-    <t>0000118237</t>
-  </si>
-  <si>
-    <t>0000118238</t>
-  </si>
-  <si>
-    <t>0000014043</t>
-  </si>
-  <si>
-    <t>REC16442132ARQ</t>
-  </si>
-  <si>
-    <t>0000118239</t>
-  </si>
-  <si>
-    <t>BLF068</t>
-  </si>
-  <si>
-    <t>REC16442129ARQ</t>
-  </si>
-  <si>
-    <t>0000118240</t>
-  </si>
-  <si>
-    <t>0000014066</t>
-  </si>
-  <si>
-    <t>REC16442128ARQ</t>
-  </si>
-  <si>
-    <t>0000118241</t>
-  </si>
-  <si>
-    <t>0000118242</t>
-  </si>
-  <si>
-    <t>0000013467</t>
-  </si>
-  <si>
     <t>BLD074</t>
   </si>
   <si>
-    <t>REC1DPULOV1025ARQ</t>
-  </si>
-  <si>
-    <t>10226441</t>
-  </si>
-  <si>
-    <t>0000118243</t>
-  </si>
-  <si>
-    <t>0000118244</t>
-  </si>
-  <si>
-    <t>BLE032</t>
-  </si>
-  <si>
-    <t>RECF05QS7443ARQ</t>
-  </si>
-  <si>
-    <t>In Process</t>
-  </si>
-  <si>
-    <t>0000118245</t>
-  </si>
-  <si>
-    <t>0000118246</t>
-  </si>
-  <si>
-    <t>0000013843</t>
-  </si>
-  <si>
-    <t>BLF061</t>
-  </si>
-  <si>
-    <t>RECF05QS7470ARQ</t>
-  </si>
-  <si>
-    <t>0000118247</t>
-  </si>
-  <si>
-    <t>0000118248</t>
-  </si>
-  <si>
-    <t>0000013841</t>
-  </si>
-  <si>
-    <t>BLH087</t>
-  </si>
-  <si>
-    <t>RECF05QS7473ARQ</t>
-  </si>
-  <si>
-    <t>0000118249</t>
-  </si>
-  <si>
-    <t>0000013851</t>
-  </si>
-  <si>
-    <t>BLE003</t>
-  </si>
-  <si>
-    <t>RECF05QS7455ARQ</t>
-  </si>
-  <si>
-    <t>10226420</t>
-  </si>
-  <si>
-    <t>0000118250</t>
-  </si>
-  <si>
-    <t>REC3259927753118ARQ</t>
-  </si>
-  <si>
-    <t>0000118251</t>
-  </si>
-  <si>
-    <t>0000013870</t>
-  </si>
-  <si>
-    <t>BLH052</t>
-  </si>
-  <si>
-    <t>RECF05QS7442ARQ</t>
-  </si>
-  <si>
-    <t>0000118252</t>
-  </si>
-  <si>
-    <t>0000013883</t>
-  </si>
-  <si>
-    <t>BLH054</t>
-  </si>
-  <si>
-    <t>RECF05QS7439ARQ</t>
-  </si>
-  <si>
-    <t>340.00000</t>
-  </si>
-  <si>
-    <t>0000118253</t>
-  </si>
-  <si>
-    <t>0000013706</t>
-  </si>
-  <si>
-    <t>BLE024</t>
-  </si>
-  <si>
-    <t>RECF05QS7536ARQ</t>
-  </si>
-  <si>
-    <t>220.00000</t>
-  </si>
-  <si>
-    <t>0000118254</t>
-  </si>
-  <si>
-    <t>0000013837</t>
-  </si>
-  <si>
-    <t>BLH078</t>
-  </si>
-  <si>
-    <t>REC3259927753095ARQ</t>
-  </si>
-  <si>
-    <t>0000118255</t>
-  </si>
-  <si>
-    <t>0000011775</t>
-  </si>
-  <si>
-    <t>BLE045</t>
-  </si>
-  <si>
-    <t>RECOWSEI5975ARQ</t>
-  </si>
-  <si>
-    <t>180.00000</t>
-  </si>
-  <si>
-    <t>0000118256</t>
-  </si>
-  <si>
-    <t>0000013840</t>
-  </si>
-  <si>
     <t>BLF079</t>
   </si>
   <si>
-    <t>REC3259927753100ARQ</t>
-  </si>
-  <si>
-    <t>0000118257</t>
-  </si>
-  <si>
-    <t>BLG084</t>
-  </si>
-  <si>
-    <t>RECF05QS7419ARQ</t>
-  </si>
-  <si>
-    <t>0000118258</t>
-  </si>
-  <si>
-    <t>0000118259</t>
-  </si>
-  <si>
-    <t>0000118260</t>
-  </si>
-  <si>
     <t>0000013942</t>
   </si>
   <si>
@@ -908,67 +275,460 @@
     <t>RECF05QS7387ARQ</t>
   </si>
   <si>
-    <t>0000118261</t>
-  </si>
-  <si>
-    <t>0000013436</t>
-  </si>
-  <si>
     <t>BLF051</t>
   </si>
   <si>
-    <t>REC1DPULOU918ARQ</t>
-  </si>
-  <si>
-    <t>10226388</t>
-  </si>
-  <si>
-    <t>0000118262</t>
-  </si>
-  <si>
-    <t>0000012543</t>
-  </si>
-  <si>
-    <t>BLG053</t>
-  </si>
-  <si>
-    <t>REC125366M1660ARQ</t>
-  </si>
-  <si>
-    <t>0000118263</t>
-  </si>
-  <si>
-    <t>0000012647</t>
-  </si>
-  <si>
-    <t>REC125366L1544ARQ</t>
-  </si>
-  <si>
-    <t>0000118264</t>
-  </si>
-  <si>
-    <t>160.00000</t>
-  </si>
-  <si>
-    <t>0000118265</t>
-  </si>
-  <si>
-    <t>0000013088</t>
-  </si>
-  <si>
-    <t>BLE025</t>
-  </si>
-  <si>
-    <t>REC1DPULP71599ARQ</t>
-  </si>
-  <si>
-    <t>0000118266</t>
-  </si>
-  <si>
-    <t>REC1DPULP71589ARQ</t>
-  </si>
-  <si>
-    <t>0000118267</t>
+    <t>6878309021</t>
+  </si>
+  <si>
+    <t>0000125351</t>
+  </si>
+  <si>
+    <t>0000014742</t>
+  </si>
+  <si>
+    <t>FR.01.01.01.02</t>
+  </si>
+  <si>
+    <t>10226421</t>
+  </si>
+  <si>
+    <t>0000001999</t>
+  </si>
+  <si>
+    <t>0000125361</t>
+  </si>
+  <si>
+    <t>0000014733</t>
+  </si>
+  <si>
+    <t>BLE048</t>
+  </si>
+  <si>
+    <t>REC99821044ARQ</t>
+  </si>
+  <si>
+    <t>10242292</t>
+  </si>
+  <si>
+    <t>0000125477</t>
+  </si>
+  <si>
+    <t>0000014707</t>
+  </si>
+  <si>
+    <t>BLE066</t>
+  </si>
+  <si>
+    <t>REC99821059ARQ</t>
+  </si>
+  <si>
+    <t>0000125478</t>
+  </si>
+  <si>
+    <t>0000014731</t>
+  </si>
+  <si>
+    <t>BLE069</t>
+  </si>
+  <si>
+    <t>REC99821060ARQ</t>
+  </si>
+  <si>
+    <t>0000125479</t>
+  </si>
+  <si>
+    <t>0000014585</t>
+  </si>
+  <si>
+    <t>REC01907296ARQ</t>
+  </si>
+  <si>
+    <t>0000125480</t>
+  </si>
+  <si>
+    <t>0000014545</t>
+  </si>
+  <si>
+    <t>BLF054</t>
+  </si>
+  <si>
+    <t>RECX72KOJ022ARQ</t>
+  </si>
+  <si>
+    <t>0000125481</t>
+  </si>
+  <si>
+    <t>0000014611</t>
+  </si>
+  <si>
+    <t>RECX72KOJ023ARQ</t>
+  </si>
+  <si>
+    <t>0000125482</t>
+  </si>
+  <si>
+    <t>0000014596</t>
+  </si>
+  <si>
+    <t>BLF056</t>
+  </si>
+  <si>
+    <t>REC01907294ARQ</t>
+  </si>
+  <si>
+    <t>0000125483</t>
+  </si>
+  <si>
+    <t>0000014597</t>
+  </si>
+  <si>
+    <t>REC01907293ARQ</t>
+  </si>
+  <si>
+    <t>0000125484</t>
+  </si>
+  <si>
+    <t>0000014552</t>
+  </si>
+  <si>
+    <t>BLF070</t>
+  </si>
+  <si>
+    <t>REC01907226ARQ</t>
+  </si>
+  <si>
+    <t>0000125485</t>
+  </si>
+  <si>
+    <t>0000014547</t>
+  </si>
+  <si>
+    <t>BLF072</t>
+  </si>
+  <si>
+    <t>REC01907276ARQ</t>
+  </si>
+  <si>
+    <t>0000125486</t>
+  </si>
+  <si>
+    <t>0000014566</t>
+  </si>
+  <si>
+    <t>REC01907273ARQ</t>
+  </si>
+  <si>
+    <t>0000125487</t>
+  </si>
+  <si>
+    <t>0000014761</t>
+  </si>
+  <si>
+    <t>BLF088</t>
+  </si>
+  <si>
+    <t>REC99821035ARQ</t>
+  </si>
+  <si>
+    <t>0000125488</t>
+  </si>
+  <si>
+    <t>0000014560</t>
+  </si>
+  <si>
+    <t>BLF090</t>
+  </si>
+  <si>
+    <t>REC01907235ARQ</t>
+  </si>
+  <si>
+    <t>0000125489</t>
+  </si>
+  <si>
+    <t>0000014571</t>
+  </si>
+  <si>
+    <t>REC01907278ARQ</t>
+  </si>
+  <si>
+    <t>0000125490</t>
+  </si>
+  <si>
+    <t>0000014414</t>
+  </si>
+  <si>
+    <t>BLG024</t>
+  </si>
+  <si>
+    <t>RECN9UH94080ARQ</t>
+  </si>
+  <si>
+    <t>0000125491</t>
+  </si>
+  <si>
+    <t>0000014318</t>
+  </si>
+  <si>
+    <t>BLG028</t>
+  </si>
+  <si>
+    <t>RECN9UH94070ARQ</t>
+  </si>
+  <si>
+    <t>0000125492</t>
+  </si>
+  <si>
+    <t>0000014370</t>
+  </si>
+  <si>
+    <t>RECN9UH94071ARQ</t>
+  </si>
+  <si>
+    <t>0000125493</t>
+  </si>
+  <si>
+    <t>0000014128</t>
+  </si>
+  <si>
+    <t>BLE013</t>
+  </si>
+  <si>
+    <t>RECN9UH94280ARQ</t>
+  </si>
+  <si>
+    <t>10226422</t>
+  </si>
+  <si>
+    <t>0000125494</t>
+  </si>
+  <si>
+    <t>0000014744</t>
+  </si>
+  <si>
+    <t>BLD081</t>
+  </si>
+  <si>
+    <t>REC99821038ARQ</t>
+  </si>
+  <si>
+    <t>0000125495</t>
+  </si>
+  <si>
+    <t>0000013945</t>
+  </si>
+  <si>
+    <t>BLG025</t>
+  </si>
+  <si>
+    <t>RECF05QS7384ARQ</t>
+  </si>
+  <si>
+    <t>10226374</t>
+  </si>
+  <si>
+    <t>270.00000</t>
+  </si>
+  <si>
+    <t>0000125496</t>
+  </si>
+  <si>
+    <t>0000014137</t>
+  </si>
+  <si>
+    <t>RECN9UH94260ARQ</t>
+  </si>
+  <si>
+    <t>0000125497</t>
+  </si>
+  <si>
+    <t>0000014543</t>
+  </si>
+  <si>
+    <t>BLF053</t>
+  </si>
+  <si>
+    <t>REC01907225ARQ</t>
+  </si>
+  <si>
+    <t>10247603</t>
+  </si>
+  <si>
+    <t>0000125498</t>
+  </si>
+  <si>
+    <t>0000014519</t>
+  </si>
+  <si>
+    <t>BLG013</t>
+  </si>
+  <si>
+    <t>REC01907205ARQ</t>
+  </si>
+  <si>
+    <t>10226368</t>
+  </si>
+  <si>
+    <t>360.00000</t>
+  </si>
+  <si>
+    <t>0000125499</t>
+  </si>
+  <si>
+    <t>0000014511</t>
+  </si>
+  <si>
+    <t>BLG014</t>
+  </si>
+  <si>
+    <t>REC01907212ARQ</t>
+  </si>
+  <si>
+    <t>0000125500</t>
+  </si>
+  <si>
+    <t>0000014561</t>
+  </si>
+  <si>
+    <t>REC01907271ARQ</t>
+  </si>
+  <si>
+    <t>0000125501</t>
+  </si>
+  <si>
+    <t>0000125502</t>
+  </si>
+  <si>
+    <t>0000014590</t>
+  </si>
+  <si>
+    <t>BLD069</t>
+  </si>
+  <si>
+    <t>REC99821054ARQ</t>
+  </si>
+  <si>
+    <t>10226398</t>
+  </si>
+  <si>
+    <t>240.00000</t>
+  </si>
+  <si>
+    <t>0000125503</t>
+  </si>
+  <si>
+    <t>0000013844</t>
+  </si>
+  <si>
+    <t>BLD086</t>
+  </si>
+  <si>
+    <t>RECF05QS7469ARQ</t>
+  </si>
+  <si>
+    <t>0000125504</t>
+  </si>
+  <si>
+    <t>0000014316</t>
+  </si>
+  <si>
+    <t>BLE029</t>
+  </si>
+  <si>
+    <t>RECN9UH94088ARQ</t>
+  </si>
+  <si>
+    <t>0000125505</t>
+  </si>
+  <si>
+    <t>0000013078</t>
+  </si>
+  <si>
+    <t>BLF004</t>
+  </si>
+  <si>
+    <t>REC1DPULP81794ARQ</t>
+  </si>
+  <si>
+    <t>0000125506</t>
+  </si>
+  <si>
+    <t>0000013079</t>
+  </si>
+  <si>
+    <t>REC1DPULP81793ARQ</t>
+  </si>
+  <si>
+    <t>0000125507</t>
+  </si>
+  <si>
+    <t>0000013087</t>
+  </si>
+  <si>
+    <t>BLF075</t>
+  </si>
+  <si>
+    <t>REC1DPULP71580ARQ</t>
+  </si>
+  <si>
+    <t>0000125508</t>
+  </si>
+  <si>
+    <t>0000013892</t>
+  </si>
+  <si>
+    <t>BLG019</t>
+  </si>
+  <si>
+    <t>RECF05QS7430ARQ</t>
+  </si>
+  <si>
+    <t>10226373</t>
+  </si>
+  <si>
+    <t>0000125509</t>
+  </si>
+  <si>
+    <t>0000013895</t>
+  </si>
+  <si>
+    <t>RECF05QS7427ARQ</t>
+  </si>
+  <si>
+    <t>0000125510</t>
+  </si>
+  <si>
+    <t>0000014125</t>
+  </si>
+  <si>
+    <t>BLG039</t>
+  </si>
+  <si>
+    <t>REC16442070ARQ</t>
+  </si>
+  <si>
+    <t>0000125511</t>
+  </si>
+  <si>
+    <t>0000013903</t>
+  </si>
+  <si>
+    <t>BLG047</t>
+  </si>
+  <si>
+    <t>RECF05QS7392ARQ</t>
+  </si>
+  <si>
+    <t>0000125512</t>
+  </si>
+  <si>
+    <t>RECF05QS7397ARQ</t>
+  </si>
+  <si>
+    <t>Aberto</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
 </sst>
 </file>
@@ -1037,7 +797,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -1089,11 +849,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -1144,6 +913,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1151,7 +926,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="20">
+  <dxfs count="22">
     <dxf>
       <border>
         <left style="thin">
@@ -1169,6 +944,26 @@
         <vertical/>
         <horizontal/>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -1691,7 +1486,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:N48"/>
+  <dimension ref="A1:N39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="14" width="19.5703125" customWidth="1"/>
@@ -1743,2070 +1538,1674 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>174</v>
+        <v>79</v>
       </c>
       <c r="B2" t="s">
-        <v>84</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s">
-        <v>175</v>
+        <v>80</v>
       </c>
       <c r="D2" t="s">
-        <v>176</v>
+        <v>81</v>
       </c>
       <c r="E2" t="s">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="F2" t="s">
-        <v>178</v>
+        <v>72</v>
       </c>
       <c r="G2" t="s">
         <v>15</v>
       </c>
       <c r="H2" t="s">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="I2" t="s">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="J2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K2" t="s">
+        <v>72</v>
+      </c>
+      <c r="L2" t="s">
+        <v>84</v>
+      </c>
+      <c r="M2" t="s">
         <v>18</v>
       </c>
-      <c r="K2" t="s">
-        <v>178</v>
-      </c>
-      <c r="L2" t="s">
-        <v>179</v>
-      </c>
-      <c r="M2" t="s">
-        <v>20</v>
-      </c>
       <c r="N2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>174</v>
+        <v>79</v>
       </c>
       <c r="B3" t="s">
-        <v>116</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>180</v>
+        <v>85</v>
       </c>
       <c r="D3" t="s">
-        <v>181</v>
+        <v>86</v>
       </c>
       <c r="E3" t="s">
-        <v>182</v>
+        <v>87</v>
       </c>
       <c r="F3" t="s">
-        <v>178</v>
+        <v>88</v>
       </c>
       <c r="G3" t="s">
         <v>15</v>
       </c>
       <c r="H3" t="s">
-        <v>125</v>
+        <v>89</v>
       </c>
       <c r="I3" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="J3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L3" t="s">
+        <v>84</v>
+      </c>
+      <c r="M3" t="s">
         <v>18</v>
       </c>
-      <c r="K3" t="s">
-        <v>178</v>
-      </c>
-      <c r="L3" t="s">
-        <v>179</v>
-      </c>
-      <c r="M3" t="s">
-        <v>20</v>
-      </c>
       <c r="N3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>174</v>
+        <v>79</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>183</v>
+        <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>184</v>
+        <v>91</v>
       </c>
       <c r="E4" t="s">
-        <v>185</v>
+        <v>92</v>
       </c>
       <c r="F4" t="s">
-        <v>186</v>
+        <v>93</v>
       </c>
       <c r="G4" t="s">
         <v>15</v>
       </c>
       <c r="H4" t="s">
+        <v>89</v>
+      </c>
+      <c r="I4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J4" t="s">
         <v>16</v>
       </c>
-      <c r="I4" t="s">
-        <v>23</v>
-      </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L4" t="s">
+        <v>84</v>
+      </c>
+      <c r="M4" t="s">
         <v>18</v>
       </c>
-      <c r="K4" t="s">
+      <c r="N4" t="s">
         <v>19</v>
-      </c>
-      <c r="L4" t="s">
-        <v>179</v>
-      </c>
-      <c r="M4" t="s">
-        <v>20</v>
-      </c>
-      <c r="N4" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>174</v>
+        <v>79</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>187</v>
+        <v>94</v>
       </c>
       <c r="D5" t="s">
-        <v>188</v>
+        <v>95</v>
       </c>
       <c r="E5" t="s">
-        <v>185</v>
+        <v>96</v>
       </c>
       <c r="F5" t="s">
-        <v>189</v>
+        <v>97</v>
       </c>
       <c r="G5" t="s">
         <v>15</v>
       </c>
       <c r="H5" t="s">
+        <v>89</v>
+      </c>
+      <c r="I5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5" t="s">
         <v>16</v>
       </c>
-      <c r="I5" t="s">
-        <v>23</v>
-      </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L5" t="s">
+        <v>84</v>
+      </c>
+      <c r="M5" t="s">
         <v>18</v>
       </c>
-      <c r="K5" t="s">
+      <c r="N5" t="s">
         <v>19</v>
-      </c>
-      <c r="L5" t="s">
-        <v>179</v>
-      </c>
-      <c r="M5" t="s">
-        <v>20</v>
-      </c>
-      <c r="N5" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>174</v>
+        <v>79</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>190</v>
+        <v>98</v>
       </c>
       <c r="D6" t="s">
-        <v>191</v>
+        <v>99</v>
       </c>
       <c r="E6" t="s">
-        <v>192</v>
+        <v>78</v>
       </c>
       <c r="F6" t="s">
-        <v>193</v>
+        <v>100</v>
       </c>
       <c r="G6" t="s">
         <v>15</v>
       </c>
       <c r="H6" t="s">
+        <v>89</v>
+      </c>
+      <c r="I6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J6" t="s">
         <v>16</v>
       </c>
-      <c r="I6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J6" t="s">
+      <c r="K6" t="s">
+        <v>17</v>
+      </c>
+      <c r="L6" t="s">
+        <v>84</v>
+      </c>
+      <c r="M6" t="s">
         <v>18</v>
       </c>
-      <c r="K6" t="s">
+      <c r="N6" t="s">
         <v>19</v>
-      </c>
-      <c r="L6" t="s">
-        <v>179</v>
-      </c>
-      <c r="M6" t="s">
-        <v>20</v>
-      </c>
-      <c r="N6" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>174</v>
+        <v>79</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>194</v>
+        <v>101</v>
       </c>
       <c r="D7" t="s">
-        <v>195</v>
+        <v>102</v>
       </c>
       <c r="E7" t="s">
-        <v>196</v>
+        <v>103</v>
       </c>
       <c r="F7" t="s">
-        <v>197</v>
+        <v>104</v>
       </c>
       <c r="G7" t="s">
         <v>15</v>
       </c>
       <c r="H7" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="I7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J7" t="s">
+        <v>16</v>
+      </c>
+      <c r="K7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L7" t="s">
+        <v>84</v>
+      </c>
+      <c r="M7" t="s">
         <v>18</v>
       </c>
-      <c r="K7" t="s">
+      <c r="N7" t="s">
         <v>19</v>
-      </c>
-      <c r="L7" t="s">
-        <v>179</v>
-      </c>
-      <c r="M7" t="s">
-        <v>20</v>
-      </c>
-      <c r="N7" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>174</v>
+        <v>79</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>198</v>
+        <v>105</v>
       </c>
       <c r="D8" t="s">
-        <v>25</v>
+        <v>106</v>
       </c>
       <c r="E8" t="s">
-        <v>26</v>
+        <v>103</v>
       </c>
       <c r="F8" t="s">
-        <v>27</v>
+        <v>107</v>
       </c>
       <c r="G8" t="s">
         <v>15</v>
       </c>
       <c r="H8" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="I8" t="s">
-        <v>64</v>
+        <v>21</v>
       </c>
       <c r="J8" t="s">
+        <v>16</v>
+      </c>
+      <c r="K8" t="s">
+        <v>17</v>
+      </c>
+      <c r="L8" t="s">
+        <v>84</v>
+      </c>
+      <c r="M8" t="s">
         <v>18</v>
       </c>
-      <c r="K8" t="s">
+      <c r="N8" t="s">
         <v>19</v>
-      </c>
-      <c r="L8" t="s">
-        <v>179</v>
-      </c>
-      <c r="M8" t="s">
-        <v>20</v>
-      </c>
-      <c r="N8" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>174</v>
+        <v>79</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>199</v>
+        <v>108</v>
       </c>
       <c r="D9" t="s">
-        <v>200</v>
+        <v>109</v>
       </c>
       <c r="E9" t="s">
-        <v>34</v>
+        <v>110</v>
       </c>
       <c r="F9" t="s">
-        <v>201</v>
+        <v>111</v>
       </c>
       <c r="G9" t="s">
         <v>15</v>
       </c>
       <c r="H9" t="s">
-        <v>32</v>
+        <v>89</v>
       </c>
       <c r="I9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J9" t="s">
+        <v>16</v>
+      </c>
+      <c r="K9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L9" t="s">
+        <v>84</v>
+      </c>
+      <c r="M9" t="s">
         <v>18</v>
       </c>
-      <c r="K9" t="s">
+      <c r="N9" t="s">
         <v>19</v>
-      </c>
-      <c r="L9" t="s">
-        <v>179</v>
-      </c>
-      <c r="M9" t="s">
-        <v>20</v>
-      </c>
-      <c r="N9" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>174</v>
+        <v>79</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>202</v>
+        <v>112</v>
       </c>
       <c r="D10" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="E10" t="s">
-        <v>203</v>
+        <v>110</v>
       </c>
       <c r="F10" t="s">
-        <v>204</v>
+        <v>114</v>
       </c>
       <c r="G10" t="s">
         <v>15</v>
       </c>
       <c r="H10" t="s">
-        <v>32</v>
+        <v>89</v>
       </c>
       <c r="I10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J10" t="s">
+        <v>16</v>
+      </c>
+      <c r="K10" t="s">
+        <v>17</v>
+      </c>
+      <c r="L10" t="s">
+        <v>84</v>
+      </c>
+      <c r="M10" t="s">
         <v>18</v>
       </c>
-      <c r="K10" t="s">
+      <c r="N10" t="s">
         <v>19</v>
-      </c>
-      <c r="L10" t="s">
-        <v>179</v>
-      </c>
-      <c r="M10" t="s">
-        <v>20</v>
-      </c>
-      <c r="N10" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>174</v>
+        <v>79</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>205</v>
+        <v>115</v>
       </c>
       <c r="D11" t="s">
-        <v>33</v>
+        <v>116</v>
       </c>
       <c r="E11" t="s">
-        <v>34</v>
+        <v>117</v>
       </c>
       <c r="F11" t="s">
-        <v>35</v>
+        <v>118</v>
       </c>
       <c r="G11" t="s">
         <v>15</v>
       </c>
       <c r="H11" t="s">
-        <v>32</v>
+        <v>89</v>
       </c>
       <c r="I11" t="s">
-        <v>113</v>
+        <v>21</v>
       </c>
       <c r="J11" t="s">
+        <v>16</v>
+      </c>
+      <c r="K11" t="s">
+        <v>17</v>
+      </c>
+      <c r="L11" t="s">
+        <v>84</v>
+      </c>
+      <c r="M11" t="s">
         <v>18</v>
       </c>
-      <c r="K11" t="s">
+      <c r="N11" t="s">
         <v>19</v>
-      </c>
-      <c r="L11" t="s">
-        <v>179</v>
-      </c>
-      <c r="M11" t="s">
-        <v>20</v>
-      </c>
-      <c r="N11" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>174</v>
+        <v>79</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="C12" t="s">
-        <v>206</v>
+        <v>119</v>
       </c>
       <c r="D12" t="s">
-        <v>37</v>
+        <v>120</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>121</v>
       </c>
       <c r="F12" t="s">
-        <v>39</v>
+        <v>122</v>
       </c>
       <c r="G12" t="s">
         <v>15</v>
       </c>
       <c r="H12" t="s">
-        <v>40</v>
+        <v>89</v>
       </c>
       <c r="I12" t="s">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="J12" t="s">
+        <v>16</v>
+      </c>
+      <c r="K12" t="s">
+        <v>17</v>
+      </c>
+      <c r="L12" t="s">
+        <v>84</v>
+      </c>
+      <c r="M12" t="s">
         <v>18</v>
       </c>
-      <c r="K12" t="s">
+      <c r="N12" t="s">
         <v>19</v>
-      </c>
-      <c r="L12" t="s">
-        <v>179</v>
-      </c>
-      <c r="M12" t="s">
-        <v>20</v>
-      </c>
-      <c r="N12" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>174</v>
+        <v>79</v>
       </c>
       <c r="B13" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C13" t="s">
-        <v>207</v>
+        <v>123</v>
       </c>
       <c r="D13" t="s">
-        <v>43</v>
+        <v>124</v>
       </c>
       <c r="E13" t="s">
-        <v>44</v>
+        <v>121</v>
       </c>
       <c r="F13" t="s">
-        <v>45</v>
+        <v>125</v>
       </c>
       <c r="G13" t="s">
         <v>15</v>
       </c>
       <c r="H13" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I13" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="J13" t="s">
+        <v>16</v>
+      </c>
+      <c r="K13" t="s">
+        <v>17</v>
+      </c>
+      <c r="L13" t="s">
+        <v>84</v>
+      </c>
+      <c r="M13" t="s">
         <v>18</v>
       </c>
-      <c r="K13" t="s">
+      <c r="N13" t="s">
         <v>19</v>
-      </c>
-      <c r="L13" t="s">
-        <v>179</v>
-      </c>
-      <c r="M13" t="s">
-        <v>20</v>
-      </c>
-      <c r="N13" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>174</v>
+        <v>79</v>
       </c>
       <c r="B14" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="C14" t="s">
-        <v>208</v>
+        <v>126</v>
       </c>
       <c r="D14" t="s">
-        <v>48</v>
+        <v>127</v>
       </c>
       <c r="E14" t="s">
-        <v>49</v>
+        <v>128</v>
       </c>
       <c r="F14" t="s">
-        <v>50</v>
+        <v>129</v>
       </c>
       <c r="G14" t="s">
         <v>15</v>
       </c>
       <c r="H14" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="I14" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J14" t="s">
+        <v>16</v>
+      </c>
+      <c r="K14" t="s">
+        <v>17</v>
+      </c>
+      <c r="L14" t="s">
+        <v>84</v>
+      </c>
+      <c r="M14" t="s">
         <v>18</v>
       </c>
-      <c r="K14" t="s">
+      <c r="N14" t="s">
         <v>19</v>
-      </c>
-      <c r="L14" t="s">
-        <v>179</v>
-      </c>
-      <c r="M14" t="s">
-        <v>20</v>
-      </c>
-      <c r="N14" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>174</v>
+        <v>79</v>
       </c>
       <c r="B15" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="C15" t="s">
-        <v>209</v>
+        <v>130</v>
       </c>
       <c r="D15" t="s">
-        <v>210</v>
+        <v>131</v>
       </c>
       <c r="E15" t="s">
-        <v>211</v>
+        <v>132</v>
       </c>
       <c r="F15" t="s">
-        <v>212</v>
+        <v>133</v>
       </c>
       <c r="G15" t="s">
         <v>15</v>
       </c>
       <c r="H15" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="I15" t="s">
-        <v>115</v>
+        <v>21</v>
       </c>
       <c r="J15" t="s">
+        <v>16</v>
+      </c>
+      <c r="K15" t="s">
+        <v>17</v>
+      </c>
+      <c r="L15" t="s">
+        <v>84</v>
+      </c>
+      <c r="M15" t="s">
         <v>18</v>
       </c>
-      <c r="K15" t="s">
+      <c r="N15" t="s">
         <v>19</v>
-      </c>
-      <c r="L15" t="s">
-        <v>179</v>
-      </c>
-      <c r="M15" t="s">
-        <v>20</v>
-      </c>
-      <c r="N15" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>174</v>
+        <v>79</v>
       </c>
       <c r="B16" t="s">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>213</v>
+        <v>134</v>
       </c>
       <c r="D16" t="s">
-        <v>54</v>
+        <v>135</v>
       </c>
       <c r="E16" t="s">
-        <v>55</v>
+        <v>132</v>
       </c>
       <c r="F16" t="s">
-        <v>56</v>
+        <v>136</v>
       </c>
       <c r="G16" t="s">
         <v>15</v>
       </c>
       <c r="H16" t="s">
-        <v>57</v>
+        <v>89</v>
       </c>
       <c r="I16" t="s">
-        <v>135</v>
+        <v>21</v>
       </c>
       <c r="J16" t="s">
+        <v>16</v>
+      </c>
+      <c r="K16" t="s">
+        <v>17</v>
+      </c>
+      <c r="L16" t="s">
+        <v>84</v>
+      </c>
+      <c r="M16" t="s">
         <v>18</v>
       </c>
-      <c r="K16" t="s">
+      <c r="N16" t="s">
         <v>19</v>
-      </c>
-      <c r="L16" t="s">
-        <v>179</v>
-      </c>
-      <c r="M16" t="s">
-        <v>20</v>
-      </c>
-      <c r="N16" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>174</v>
+        <v>79</v>
       </c>
       <c r="B17" t="s">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="C17" t="s">
-        <v>214</v>
+        <v>137</v>
       </c>
       <c r="D17" t="s">
-        <v>61</v>
+        <v>138</v>
       </c>
       <c r="E17" t="s">
-        <v>62</v>
+        <v>139</v>
       </c>
       <c r="F17" t="s">
-        <v>63</v>
+        <v>140</v>
       </c>
       <c r="G17" t="s">
         <v>15</v>
       </c>
       <c r="H17" t="s">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="I17" t="s">
-        <v>78</v>
+        <v>21</v>
       </c>
       <c r="J17" t="s">
+        <v>16</v>
+      </c>
+      <c r="K17" t="s">
+        <v>17</v>
+      </c>
+      <c r="L17" t="s">
+        <v>84</v>
+      </c>
+      <c r="M17" t="s">
         <v>18</v>
       </c>
-      <c r="K17" t="s">
+      <c r="N17" t="s">
         <v>19</v>
-      </c>
-      <c r="L17" t="s">
-        <v>179</v>
-      </c>
-      <c r="M17" t="s">
-        <v>20</v>
-      </c>
-      <c r="N17" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>174</v>
+        <v>79</v>
       </c>
       <c r="B18" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="C18" t="s">
-        <v>215</v>
+        <v>141</v>
       </c>
       <c r="D18" t="s">
-        <v>69</v>
+        <v>142</v>
       </c>
       <c r="E18" t="s">
-        <v>70</v>
+        <v>143</v>
       </c>
       <c r="F18" t="s">
-        <v>71</v>
+        <v>144</v>
       </c>
       <c r="G18" t="s">
         <v>15</v>
       </c>
       <c r="H18" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="I18" t="s">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="J18" t="s">
+        <v>16</v>
+      </c>
+      <c r="K18" t="s">
+        <v>17</v>
+      </c>
+      <c r="L18" t="s">
+        <v>84</v>
+      </c>
+      <c r="M18" t="s">
         <v>18</v>
       </c>
-      <c r="K18" t="s">
+      <c r="N18" t="s">
         <v>19</v>
-      </c>
-      <c r="L18" t="s">
-        <v>179</v>
-      </c>
-      <c r="M18" t="s">
-        <v>20</v>
-      </c>
-      <c r="N18" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>174</v>
+        <v>79</v>
       </c>
       <c r="B19" t="s">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="C19" t="s">
-        <v>216</v>
+        <v>145</v>
       </c>
       <c r="D19" t="s">
-        <v>217</v>
+        <v>146</v>
       </c>
       <c r="E19" t="s">
-        <v>74</v>
+        <v>143</v>
       </c>
       <c r="F19" t="s">
-        <v>218</v>
+        <v>147</v>
       </c>
       <c r="G19" t="s">
         <v>15</v>
       </c>
       <c r="H19" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="I19" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J19" t="s">
+        <v>16</v>
+      </c>
+      <c r="K19" t="s">
+        <v>17</v>
+      </c>
+      <c r="L19" t="s">
+        <v>84</v>
+      </c>
+      <c r="M19" t="s">
         <v>18</v>
       </c>
-      <c r="K19" t="s">
+      <c r="N19" t="s">
         <v>19</v>
-      </c>
-      <c r="L19" t="s">
-        <v>179</v>
-      </c>
-      <c r="M19" t="s">
-        <v>20</v>
-      </c>
-      <c r="N19" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>174</v>
+        <v>79</v>
       </c>
       <c r="B20" t="s">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="C20" t="s">
-        <v>219</v>
+        <v>148</v>
       </c>
       <c r="D20" t="s">
-        <v>217</v>
+        <v>149</v>
       </c>
       <c r="E20" t="s">
-        <v>220</v>
+        <v>150</v>
       </c>
       <c r="F20" t="s">
-        <v>221</v>
+        <v>151</v>
       </c>
       <c r="G20" t="s">
         <v>15</v>
       </c>
       <c r="H20" t="s">
-        <v>75</v>
+        <v>152</v>
       </c>
       <c r="I20" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J20" t="s">
+        <v>16</v>
+      </c>
+      <c r="K20" t="s">
+        <v>17</v>
+      </c>
+      <c r="L20" t="s">
+        <v>84</v>
+      </c>
+      <c r="M20" t="s">
         <v>18</v>
       </c>
-      <c r="K20" t="s">
+      <c r="N20" t="s">
         <v>19</v>
-      </c>
-      <c r="L20" t="s">
-        <v>179</v>
-      </c>
-      <c r="M20" t="s">
-        <v>20</v>
-      </c>
-      <c r="N20" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>174</v>
+        <v>79</v>
       </c>
       <c r="B21" t="s">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="C21" t="s">
-        <v>222</v>
+        <v>153</v>
       </c>
       <c r="D21" t="s">
-        <v>223</v>
+        <v>154</v>
       </c>
       <c r="E21" t="s">
-        <v>220</v>
+        <v>155</v>
       </c>
       <c r="F21" t="s">
-        <v>224</v>
+        <v>156</v>
       </c>
       <c r="G21" t="s">
         <v>15</v>
       </c>
       <c r="H21" t="s">
-        <v>75</v>
+        <v>152</v>
       </c>
       <c r="I21" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="J21" t="s">
+        <v>16</v>
+      </c>
+      <c r="K21" t="s">
+        <v>17</v>
+      </c>
+      <c r="L21" t="s">
+        <v>84</v>
+      </c>
+      <c r="M21" t="s">
         <v>18</v>
       </c>
-      <c r="K21" t="s">
+      <c r="N21" t="s">
         <v>19</v>
-      </c>
-      <c r="L21" t="s">
-        <v>179</v>
-      </c>
-      <c r="M21" t="s">
-        <v>20</v>
-      </c>
-      <c r="N21" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>174</v>
+        <v>79</v>
       </c>
       <c r="B22" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="C22" t="s">
-        <v>225</v>
+        <v>157</v>
       </c>
       <c r="D22" t="s">
-        <v>81</v>
+        <v>158</v>
       </c>
       <c r="E22" t="s">
-        <v>82</v>
+        <v>159</v>
       </c>
       <c r="F22" t="s">
-        <v>83</v>
+        <v>160</v>
       </c>
       <c r="G22" t="s">
         <v>15</v>
       </c>
       <c r="H22" t="s">
-        <v>80</v>
+        <v>161</v>
       </c>
       <c r="I22" t="s">
-        <v>52</v>
+        <v>162</v>
       </c>
       <c r="J22" t="s">
+        <v>16</v>
+      </c>
+      <c r="K22" t="s">
+        <v>17</v>
+      </c>
+      <c r="L22" t="s">
+        <v>84</v>
+      </c>
+      <c r="M22" t="s">
         <v>18</v>
       </c>
-      <c r="K22" t="s">
+      <c r="N22" t="s">
         <v>19</v>
-      </c>
-      <c r="L22" t="s">
-        <v>179</v>
-      </c>
-      <c r="M22" t="s">
-        <v>20</v>
-      </c>
-      <c r="N22" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>174</v>
+        <v>79</v>
       </c>
       <c r="B23" t="s">
-        <v>67</v>
+        <v>22</v>
       </c>
       <c r="C23" t="s">
-        <v>226</v>
+        <v>163</v>
       </c>
       <c r="D23" t="s">
-        <v>227</v>
+        <v>164</v>
       </c>
       <c r="E23" t="s">
-        <v>228</v>
+        <v>73</v>
       </c>
       <c r="F23" t="s">
-        <v>229</v>
+        <v>165</v>
       </c>
       <c r="G23" t="s">
         <v>15</v>
       </c>
       <c r="H23" t="s">
-        <v>230</v>
+        <v>161</v>
       </c>
       <c r="I23" t="s">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="J23" t="s">
+        <v>16</v>
+      </c>
+      <c r="K23" t="s">
+        <v>17</v>
+      </c>
+      <c r="L23" t="s">
+        <v>84</v>
+      </c>
+      <c r="M23" t="s">
         <v>18</v>
       </c>
-      <c r="K23" t="s">
+      <c r="N23" t="s">
         <v>19</v>
-      </c>
-      <c r="L23" t="s">
-        <v>179</v>
-      </c>
-      <c r="M23" t="s">
-        <v>20</v>
-      </c>
-      <c r="N23" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>174</v>
+        <v>79</v>
       </c>
       <c r="B24" t="s">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="C24" t="s">
-        <v>231</v>
+        <v>166</v>
       </c>
       <c r="D24" t="s">
-        <v>87</v>
+        <v>167</v>
       </c>
       <c r="E24" t="s">
-        <v>88</v>
+        <v>168</v>
       </c>
       <c r="F24" t="s">
-        <v>89</v>
+        <v>169</v>
       </c>
       <c r="G24" t="s">
         <v>15</v>
       </c>
       <c r="H24" t="s">
-        <v>90</v>
+        <v>170</v>
       </c>
       <c r="I24" t="s">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="J24" t="s">
+        <v>16</v>
+      </c>
+      <c r="K24" t="s">
+        <v>17</v>
+      </c>
+      <c r="L24" t="s">
+        <v>84</v>
+      </c>
+      <c r="M24" t="s">
         <v>18</v>
       </c>
-      <c r="K24" t="s">
+      <c r="N24" t="s">
         <v>19</v>
-      </c>
-      <c r="L24" t="s">
-        <v>179</v>
-      </c>
-      <c r="M24" t="s">
-        <v>20</v>
-      </c>
-      <c r="N24" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>79</v>
+      </c>
+      <c r="B25" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" t="s">
+        <v>171</v>
+      </c>
+      <c r="D25" t="s">
+        <v>172</v>
+      </c>
+      <c r="E25" t="s">
+        <v>173</v>
+      </c>
+      <c r="F25" t="s">
         <v>174</v>
-      </c>
-      <c r="B25" t="s">
-        <v>73</v>
-      </c>
-      <c r="C25" t="s">
-        <v>232</v>
-      </c>
-      <c r="D25" t="s">
-        <v>92</v>
-      </c>
-      <c r="E25" t="s">
-        <v>233</v>
-      </c>
-      <c r="F25" t="s">
-        <v>234</v>
       </c>
       <c r="G25" t="s">
         <v>15</v>
       </c>
       <c r="H25" t="s">
-        <v>93</v>
+        <v>175</v>
       </c>
       <c r="I25" t="s">
-        <v>23</v>
+        <v>176</v>
       </c>
       <c r="J25" t="s">
-        <v>235</v>
+        <v>16</v>
       </c>
       <c r="K25" t="s">
+        <v>17</v>
+      </c>
+      <c r="L25" t="s">
+        <v>84</v>
+      </c>
+      <c r="M25" t="s">
+        <v>18</v>
+      </c>
+      <c r="N25" t="s">
         <v>19</v>
-      </c>
-      <c r="L25" t="s">
-        <v>179</v>
-      </c>
-      <c r="M25" t="s">
-        <v>20</v>
-      </c>
-      <c r="N25" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>174</v>
+        <v>79</v>
       </c>
       <c r="B26" t="s">
-        <v>76</v>
+        <v>24</v>
       </c>
       <c r="C26" t="s">
-        <v>236</v>
+        <v>177</v>
       </c>
       <c r="D26" t="s">
-        <v>95</v>
+        <v>178</v>
       </c>
       <c r="E26" t="s">
-        <v>96</v>
+        <v>179</v>
       </c>
       <c r="F26" t="s">
-        <v>97</v>
+        <v>180</v>
       </c>
       <c r="G26" t="s">
         <v>15</v>
       </c>
       <c r="H26" t="s">
-        <v>98</v>
+        <v>175</v>
       </c>
       <c r="I26" t="s">
-        <v>85</v>
+        <v>176</v>
       </c>
       <c r="J26" t="s">
+        <v>16</v>
+      </c>
+      <c r="K26" t="s">
+        <v>17</v>
+      </c>
+      <c r="L26" t="s">
+        <v>84</v>
+      </c>
+      <c r="M26" t="s">
         <v>18</v>
       </c>
-      <c r="K26" t="s">
+      <c r="N26" t="s">
         <v>19</v>
-      </c>
-      <c r="L26" t="s">
-        <v>179</v>
-      </c>
-      <c r="M26" t="s">
-        <v>20</v>
-      </c>
-      <c r="N26" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>174</v>
+        <v>79</v>
       </c>
       <c r="B27" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C27" t="s">
-        <v>237</v>
+        <v>181</v>
       </c>
       <c r="D27" t="s">
-        <v>238</v>
+        <v>182</v>
       </c>
       <c r="E27" t="s">
-        <v>239</v>
+        <v>74</v>
       </c>
       <c r="F27" t="s">
-        <v>240</v>
+        <v>183</v>
       </c>
       <c r="G27" t="s">
         <v>15</v>
       </c>
       <c r="H27" t="s">
-        <v>103</v>
+        <v>175</v>
       </c>
       <c r="I27" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J27" t="s">
+        <v>16</v>
+      </c>
+      <c r="K27" t="s">
+        <v>17</v>
+      </c>
+      <c r="L27" t="s">
+        <v>84</v>
+      </c>
+      <c r="M27" t="s">
         <v>18</v>
       </c>
-      <c r="K27" t="s">
+      <c r="N27" t="s">
         <v>19</v>
-      </c>
-      <c r="L27" t="s">
-        <v>179</v>
-      </c>
-      <c r="M27" t="s">
-        <v>20</v>
-      </c>
-      <c r="N27" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>174</v>
+        <v>79</v>
       </c>
       <c r="B28" t="s">
+        <v>26</v>
+      </c>
+      <c r="C28" t="s">
+        <v>184</v>
+      </c>
+      <c r="D28" t="s">
+        <v>75</v>
+      </c>
+      <c r="E28" t="s">
+        <v>76</v>
+      </c>
+      <c r="F28" t="s">
         <v>77</v>
-      </c>
-      <c r="C28" t="s">
-        <v>241</v>
-      </c>
-      <c r="D28" t="s">
-        <v>100</v>
-      </c>
-      <c r="E28" t="s">
-        <v>101</v>
-      </c>
-      <c r="F28" t="s">
-        <v>102</v>
       </c>
       <c r="G28" t="s">
         <v>15</v>
       </c>
       <c r="H28" t="s">
-        <v>103</v>
+        <v>35</v>
       </c>
       <c r="I28" t="s">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="J28" t="s">
+        <v>16</v>
+      </c>
+      <c r="K28" t="s">
+        <v>17</v>
+      </c>
+      <c r="L28" t="s">
+        <v>84</v>
+      </c>
+      <c r="M28" t="s">
         <v>18</v>
       </c>
-      <c r="K28" t="s">
+      <c r="N28" t="s">
         <v>19</v>
-      </c>
-      <c r="L28" t="s">
-        <v>179</v>
-      </c>
-      <c r="M28" t="s">
-        <v>20</v>
-      </c>
-      <c r="N28" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>174</v>
+        <v>79</v>
       </c>
       <c r="B29" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C29" t="s">
-        <v>242</v>
+        <v>185</v>
       </c>
       <c r="D29" t="s">
-        <v>243</v>
+        <v>186</v>
       </c>
       <c r="E29" t="s">
-        <v>244</v>
+        <v>187</v>
       </c>
       <c r="F29" t="s">
-        <v>245</v>
+        <v>188</v>
       </c>
       <c r="G29" t="s">
         <v>15</v>
       </c>
       <c r="H29" t="s">
-        <v>103</v>
+        <v>189</v>
       </c>
       <c r="I29" t="s">
-        <v>113</v>
+        <v>190</v>
       </c>
       <c r="J29" t="s">
+        <v>16</v>
+      </c>
+      <c r="K29" t="s">
+        <v>17</v>
+      </c>
+      <c r="L29" t="s">
+        <v>84</v>
+      </c>
+      <c r="M29" t="s">
         <v>18</v>
       </c>
-      <c r="K29" t="s">
+      <c r="N29" t="s">
         <v>19</v>
-      </c>
-      <c r="L29" t="s">
-        <v>179</v>
-      </c>
-      <c r="M29" t="s">
-        <v>20</v>
-      </c>
-      <c r="N29" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>174</v>
+        <v>79</v>
       </c>
       <c r="B30" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="C30" t="s">
-        <v>246</v>
+        <v>191</v>
       </c>
       <c r="D30" t="s">
-        <v>247</v>
+        <v>192</v>
       </c>
       <c r="E30" t="s">
-        <v>248</v>
+        <v>193</v>
       </c>
       <c r="F30" t="s">
-        <v>249</v>
+        <v>194</v>
       </c>
       <c r="G30" t="s">
         <v>15</v>
       </c>
       <c r="H30" t="s">
-        <v>250</v>
+        <v>189</v>
       </c>
       <c r="I30" t="s">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="J30" t="s">
+        <v>16</v>
+      </c>
+      <c r="K30" t="s">
+        <v>17</v>
+      </c>
+      <c r="L30" t="s">
+        <v>84</v>
+      </c>
+      <c r="M30" t="s">
         <v>18</v>
       </c>
-      <c r="K30" t="s">
+      <c r="N30" t="s">
         <v>19</v>
-      </c>
-      <c r="L30" t="s">
-        <v>179</v>
-      </c>
-      <c r="M30" t="s">
-        <v>20</v>
-      </c>
-      <c r="N30" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>174</v>
+        <v>79</v>
       </c>
       <c r="B31" t="s">
-        <v>84</v>
+        <v>27</v>
       </c>
       <c r="C31" t="s">
-        <v>251</v>
+        <v>195</v>
       </c>
       <c r="D31" t="s">
-        <v>107</v>
+        <v>196</v>
       </c>
       <c r="E31" t="s">
-        <v>108</v>
+        <v>197</v>
       </c>
       <c r="F31" t="s">
-        <v>252</v>
+        <v>198</v>
       </c>
       <c r="G31" t="s">
         <v>15</v>
       </c>
       <c r="H31" t="s">
-        <v>106</v>
+        <v>189</v>
       </c>
       <c r="I31" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J31" t="s">
+        <v>16</v>
+      </c>
+      <c r="K31" t="s">
+        <v>17</v>
+      </c>
+      <c r="L31" t="s">
+        <v>84</v>
+      </c>
+      <c r="M31" t="s">
         <v>18</v>
       </c>
-      <c r="K31" t="s">
+      <c r="N31" t="s">
         <v>19</v>
-      </c>
-      <c r="L31" t="s">
-        <v>179</v>
-      </c>
-      <c r="M31" t="s">
-        <v>20</v>
-      </c>
-      <c r="N31" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>174</v>
+        <v>79</v>
       </c>
       <c r="B32" t="s">
-        <v>84</v>
+        <v>29</v>
       </c>
       <c r="C32" t="s">
-        <v>253</v>
+        <v>199</v>
       </c>
       <c r="D32" t="s">
-        <v>254</v>
+        <v>200</v>
       </c>
       <c r="E32" t="s">
-        <v>255</v>
+        <v>201</v>
       </c>
       <c r="F32" t="s">
-        <v>256</v>
+        <v>202</v>
       </c>
       <c r="G32" t="s">
         <v>15</v>
       </c>
       <c r="H32" t="s">
-        <v>106</v>
+        <v>36</v>
       </c>
       <c r="I32" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J32" t="s">
+        <v>16</v>
+      </c>
+      <c r="K32" t="s">
+        <v>17</v>
+      </c>
+      <c r="L32" t="s">
+        <v>84</v>
+      </c>
+      <c r="M32" t="s">
         <v>18</v>
       </c>
-      <c r="K32" t="s">
+      <c r="N32" t="s">
         <v>19</v>
-      </c>
-      <c r="L32" t="s">
-        <v>179</v>
-      </c>
-      <c r="M32" t="s">
-        <v>20</v>
-      </c>
-      <c r="N32" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>174</v>
+        <v>79</v>
       </c>
       <c r="B33" t="s">
-        <v>84</v>
+        <v>29</v>
       </c>
       <c r="C33" t="s">
-        <v>257</v>
+        <v>203</v>
       </c>
       <c r="D33" t="s">
-        <v>258</v>
+        <v>204</v>
       </c>
       <c r="E33" t="s">
-        <v>259</v>
+        <v>201</v>
       </c>
       <c r="F33" t="s">
-        <v>260</v>
+        <v>205</v>
       </c>
       <c r="G33" t="s">
         <v>15</v>
       </c>
       <c r="H33" t="s">
-        <v>106</v>
+        <v>36</v>
       </c>
       <c r="I33" t="s">
-        <v>261</v>
+        <v>21</v>
       </c>
       <c r="J33" t="s">
+        <v>16</v>
+      </c>
+      <c r="K33" t="s">
+        <v>17</v>
+      </c>
+      <c r="L33" t="s">
+        <v>84</v>
+      </c>
+      <c r="M33" t="s">
         <v>18</v>
       </c>
-      <c r="K33" t="s">
+      <c r="N33" t="s">
         <v>19</v>
-      </c>
-      <c r="L33" t="s">
-        <v>179</v>
-      </c>
-      <c r="M33" t="s">
-        <v>20</v>
-      </c>
-      <c r="N33" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>174</v>
+        <v>79</v>
       </c>
       <c r="B34" t="s">
-        <v>84</v>
+        <v>29</v>
       </c>
       <c r="C34" t="s">
-        <v>262</v>
+        <v>206</v>
       </c>
       <c r="D34" t="s">
-        <v>263</v>
+        <v>207</v>
       </c>
       <c r="E34" t="s">
-        <v>264</v>
+        <v>208</v>
       </c>
       <c r="F34" t="s">
-        <v>265</v>
+        <v>209</v>
       </c>
       <c r="G34" t="s">
         <v>15</v>
       </c>
       <c r="H34" t="s">
-        <v>106</v>
+        <v>36</v>
       </c>
       <c r="I34" t="s">
-        <v>266</v>
+        <v>21</v>
       </c>
       <c r="J34" t="s">
+        <v>16</v>
+      </c>
+      <c r="K34" t="s">
+        <v>17</v>
+      </c>
+      <c r="L34" t="s">
+        <v>84</v>
+      </c>
+      <c r="M34" t="s">
         <v>18</v>
       </c>
-      <c r="K34" t="s">
+      <c r="N34" t="s">
         <v>19</v>
-      </c>
-      <c r="L34" t="s">
-        <v>179</v>
-      </c>
-      <c r="M34" t="s">
-        <v>20</v>
-      </c>
-      <c r="N34" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>174</v>
+        <v>79</v>
       </c>
       <c r="B35" t="s">
-        <v>86</v>
+        <v>32</v>
       </c>
       <c r="C35" t="s">
-        <v>267</v>
+        <v>210</v>
       </c>
       <c r="D35" t="s">
-        <v>268</v>
+        <v>211</v>
       </c>
       <c r="E35" t="s">
-        <v>269</v>
+        <v>212</v>
       </c>
       <c r="F35" t="s">
-        <v>270</v>
+        <v>213</v>
       </c>
       <c r="G35" t="s">
         <v>15</v>
       </c>
       <c r="H35" t="s">
-        <v>110</v>
+        <v>214</v>
       </c>
       <c r="I35" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J35" t="s">
+        <v>16</v>
+      </c>
+      <c r="K35" t="s">
+        <v>17</v>
+      </c>
+      <c r="L35" t="s">
+        <v>84</v>
+      </c>
+      <c r="M35" t="s">
         <v>18</v>
       </c>
-      <c r="K35" t="s">
+      <c r="N35" t="s">
         <v>19</v>
-      </c>
-      <c r="L35" t="s">
-        <v>179</v>
-      </c>
-      <c r="M35" t="s">
-        <v>20</v>
-      </c>
-      <c r="N35" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>174</v>
+        <v>79</v>
       </c>
       <c r="B36" t="s">
-        <v>86</v>
+        <v>32</v>
       </c>
       <c r="C36" t="s">
-        <v>271</v>
+        <v>215</v>
       </c>
       <c r="D36" t="s">
-        <v>272</v>
+        <v>216</v>
       </c>
       <c r="E36" t="s">
-        <v>273</v>
+        <v>212</v>
       </c>
       <c r="F36" t="s">
-        <v>274</v>
+        <v>217</v>
       </c>
       <c r="G36" t="s">
         <v>15</v>
       </c>
       <c r="H36" t="s">
-        <v>110</v>
+        <v>214</v>
       </c>
       <c r="I36" t="s">
-        <v>275</v>
+        <v>21</v>
       </c>
       <c r="J36" t="s">
+        <v>16</v>
+      </c>
+      <c r="K36" t="s">
+        <v>17</v>
+      </c>
+      <c r="L36" t="s">
+        <v>84</v>
+      </c>
+      <c r="M36" t="s">
         <v>18</v>
       </c>
-      <c r="K36" t="s">
+      <c r="N36" t="s">
         <v>19</v>
-      </c>
-      <c r="L36" t="s">
-        <v>179</v>
-      </c>
-      <c r="M36" t="s">
-        <v>20</v>
-      </c>
-      <c r="N36" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>174</v>
+        <v>79</v>
       </c>
       <c r="B37" t="s">
-        <v>86</v>
+        <v>32</v>
       </c>
       <c r="C37" t="s">
-        <v>276</v>
+        <v>218</v>
       </c>
       <c r="D37" t="s">
-        <v>277</v>
+        <v>219</v>
       </c>
       <c r="E37" t="s">
-        <v>278</v>
+        <v>220</v>
       </c>
       <c r="F37" t="s">
-        <v>279</v>
+        <v>221</v>
       </c>
       <c r="G37" t="s">
         <v>15</v>
       </c>
       <c r="H37" t="s">
-        <v>110</v>
+        <v>214</v>
       </c>
       <c r="I37" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="J37" t="s">
+        <v>16</v>
+      </c>
+      <c r="K37" t="s">
+        <v>17</v>
+      </c>
+      <c r="L37" t="s">
+        <v>84</v>
+      </c>
+      <c r="M37" t="s">
         <v>18</v>
       </c>
-      <c r="K37" t="s">
+      <c r="N37" t="s">
         <v>19</v>
-      </c>
-      <c r="L37" t="s">
-        <v>179</v>
-      </c>
-      <c r="M37" t="s">
-        <v>20</v>
-      </c>
-      <c r="N37" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>174</v>
+        <v>79</v>
       </c>
       <c r="B38" t="s">
-        <v>91</v>
+        <v>32</v>
       </c>
       <c r="C38" t="s">
-        <v>280</v>
+        <v>222</v>
       </c>
       <c r="D38" t="s">
-        <v>114</v>
+        <v>223</v>
       </c>
       <c r="E38" t="s">
-        <v>281</v>
+        <v>224</v>
       </c>
       <c r="F38" t="s">
-        <v>282</v>
+        <v>225</v>
       </c>
       <c r="G38" t="s">
         <v>15</v>
       </c>
       <c r="H38" t="s">
-        <v>112</v>
+        <v>214</v>
       </c>
       <c r="I38" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J38" t="s">
+        <v>16</v>
+      </c>
+      <c r="K38" t="s">
+        <v>17</v>
+      </c>
+      <c r="L38" t="s">
+        <v>84</v>
+      </c>
+      <c r="M38" t="s">
         <v>18</v>
       </c>
-      <c r="K38" t="s">
+      <c r="N38" t="s">
         <v>19</v>
-      </c>
-      <c r="L38" t="s">
-        <v>179</v>
-      </c>
-      <c r="M38" t="s">
-        <v>20</v>
-      </c>
-      <c r="N38" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>174</v>
+        <v>79</v>
       </c>
       <c r="B39" t="s">
-        <v>94</v>
+        <v>32</v>
       </c>
       <c r="C39" t="s">
-        <v>283</v>
+        <v>226</v>
       </c>
       <c r="D39" t="s">
-        <v>117</v>
+        <v>223</v>
       </c>
       <c r="E39" t="s">
-        <v>118</v>
+        <v>224</v>
       </c>
       <c r="F39" t="s">
-        <v>119</v>
+        <v>227</v>
       </c>
       <c r="G39" t="s">
         <v>15</v>
       </c>
       <c r="H39" t="s">
-        <v>120</v>
+        <v>214</v>
       </c>
       <c r="I39" t="s">
-        <v>85</v>
+        <v>21</v>
       </c>
       <c r="J39" t="s">
+        <v>16</v>
+      </c>
+      <c r="K39" t="s">
+        <v>17</v>
+      </c>
+      <c r="L39" t="s">
+        <v>84</v>
+      </c>
+      <c r="M39" t="s">
         <v>18</v>
       </c>
-      <c r="K39" t="s">
+      <c r="N39" t="s">
         <v>19</v>
-      </c>
-      <c r="L39" t="s">
-        <v>179</v>
-      </c>
-      <c r="M39" t="s">
-        <v>20</v>
-      </c>
-      <c r="N39" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>174</v>
-      </c>
-      <c r="B40" t="s">
-        <v>99</v>
-      </c>
-      <c r="C40" t="s">
-        <v>284</v>
-      </c>
-      <c r="D40" t="s">
-        <v>121</v>
-      </c>
-      <c r="E40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F40" t="s">
-        <v>123</v>
-      </c>
-      <c r="G40" t="s">
-        <v>15</v>
-      </c>
-      <c r="H40" t="s">
-        <v>124</v>
-      </c>
-      <c r="I40" t="s">
-        <v>60</v>
-      </c>
-      <c r="J40" t="s">
-        <v>18</v>
-      </c>
-      <c r="K40" t="s">
-        <v>19</v>
-      </c>
-      <c r="L40" t="s">
-        <v>179</v>
-      </c>
-      <c r="M40" t="s">
-        <v>20</v>
-      </c>
-      <c r="N40" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>174</v>
-      </c>
-      <c r="B41" t="s">
-        <v>99</v>
-      </c>
-      <c r="C41" t="s">
-        <v>285</v>
-      </c>
-      <c r="D41" t="s">
-        <v>286</v>
-      </c>
-      <c r="E41" t="s">
-        <v>287</v>
-      </c>
-      <c r="F41" t="s">
-        <v>288</v>
-      </c>
-      <c r="G41" t="s">
-        <v>15</v>
-      </c>
-      <c r="H41" t="s">
-        <v>124</v>
-      </c>
-      <c r="I41" t="s">
-        <v>130</v>
-      </c>
-      <c r="J41" t="s">
-        <v>18</v>
-      </c>
-      <c r="K41" t="s">
-        <v>19</v>
-      </c>
-      <c r="L41" t="s">
-        <v>179</v>
-      </c>
-      <c r="M41" t="s">
-        <v>20</v>
-      </c>
-      <c r="N41" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>174</v>
-      </c>
-      <c r="B42" t="s">
-        <v>104</v>
-      </c>
-      <c r="C42" t="s">
-        <v>289</v>
-      </c>
-      <c r="D42" t="s">
-        <v>290</v>
-      </c>
-      <c r="E42" t="s">
-        <v>291</v>
-      </c>
-      <c r="F42" t="s">
-        <v>292</v>
-      </c>
-      <c r="G42" t="s">
-        <v>15</v>
-      </c>
-      <c r="H42" t="s">
-        <v>293</v>
-      </c>
-      <c r="I42" t="s">
-        <v>64</v>
-      </c>
-      <c r="J42" t="s">
-        <v>18</v>
-      </c>
-      <c r="K42" t="s">
-        <v>19</v>
-      </c>
-      <c r="L42" t="s">
-        <v>179</v>
-      </c>
-      <c r="M42" t="s">
-        <v>20</v>
-      </c>
-      <c r="N42" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>174</v>
-      </c>
-      <c r="B43" t="s">
-        <v>105</v>
-      </c>
-      <c r="C43" t="s">
-        <v>294</v>
-      </c>
-      <c r="D43" t="s">
-        <v>295</v>
-      </c>
-      <c r="E43" t="s">
-        <v>296</v>
-      </c>
-      <c r="F43" t="s">
-        <v>297</v>
-      </c>
-      <c r="G43" t="s">
-        <v>15</v>
-      </c>
-      <c r="H43" t="s">
-        <v>129</v>
-      </c>
-      <c r="I43" t="s">
-        <v>23</v>
-      </c>
-      <c r="J43" t="s">
-        <v>18</v>
-      </c>
-      <c r="K43" t="s">
-        <v>19</v>
-      </c>
-      <c r="L43" t="s">
-        <v>179</v>
-      </c>
-      <c r="M43" t="s">
-        <v>20</v>
-      </c>
-      <c r="N43" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>174</v>
-      </c>
-      <c r="B44" t="s">
-        <v>105</v>
-      </c>
-      <c r="C44" t="s">
-        <v>298</v>
-      </c>
-      <c r="D44" t="s">
-        <v>299</v>
-      </c>
-      <c r="E44" t="s">
-        <v>296</v>
-      </c>
-      <c r="F44" t="s">
-        <v>300</v>
-      </c>
-      <c r="G44" t="s">
-        <v>15</v>
-      </c>
-      <c r="H44" t="s">
-        <v>129</v>
-      </c>
-      <c r="I44" t="s">
-        <v>23</v>
-      </c>
-      <c r="J44" t="s">
-        <v>18</v>
-      </c>
-      <c r="K44" t="s">
-        <v>19</v>
-      </c>
-      <c r="L44" t="s">
-        <v>179</v>
-      </c>
-      <c r="M44" t="s">
-        <v>20</v>
-      </c>
-      <c r="N44" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>174</v>
-      </c>
-      <c r="B45" t="s">
-        <v>109</v>
-      </c>
-      <c r="C45" t="s">
-        <v>301</v>
-      </c>
-      <c r="D45" t="s">
-        <v>132</v>
-      </c>
-      <c r="E45" t="s">
-        <v>133</v>
-      </c>
-      <c r="F45" t="s">
-        <v>134</v>
-      </c>
-      <c r="G45" t="s">
-        <v>15</v>
-      </c>
-      <c r="H45" t="s">
-        <v>131</v>
-      </c>
-      <c r="I45" t="s">
-        <v>302</v>
-      </c>
-      <c r="J45" t="s">
-        <v>18</v>
-      </c>
-      <c r="K45" t="s">
-        <v>19</v>
-      </c>
-      <c r="L45" t="s">
-        <v>179</v>
-      </c>
-      <c r="M45" t="s">
-        <v>20</v>
-      </c>
-      <c r="N45" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>174</v>
-      </c>
-      <c r="B46" t="s">
-        <v>111</v>
-      </c>
-      <c r="C46" t="s">
-        <v>303</v>
-      </c>
-      <c r="D46" t="s">
-        <v>304</v>
-      </c>
-      <c r="E46" t="s">
-        <v>305</v>
-      </c>
-      <c r="F46" t="s">
-        <v>306</v>
-      </c>
-      <c r="G46" t="s">
-        <v>15</v>
-      </c>
-      <c r="H46" t="s">
-        <v>137</v>
-      </c>
-      <c r="I46" t="s">
-        <v>23</v>
-      </c>
-      <c r="J46" t="s">
-        <v>235</v>
-      </c>
-      <c r="K46" t="s">
-        <v>19</v>
-      </c>
-      <c r="L46" t="s">
-        <v>179</v>
-      </c>
-      <c r="M46" t="s">
-        <v>20</v>
-      </c>
-      <c r="N46" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>174</v>
-      </c>
-      <c r="B47" t="s">
-        <v>111</v>
-      </c>
-      <c r="C47" t="s">
-        <v>307</v>
-      </c>
-      <c r="D47" t="s">
-        <v>304</v>
-      </c>
-      <c r="E47" t="s">
-        <v>136</v>
-      </c>
-      <c r="F47" t="s">
-        <v>308</v>
-      </c>
-      <c r="G47" t="s">
-        <v>15</v>
-      </c>
-      <c r="H47" t="s">
-        <v>137</v>
-      </c>
-      <c r="I47" t="s">
-        <v>23</v>
-      </c>
-      <c r="J47" t="s">
-        <v>235</v>
-      </c>
-      <c r="K47" t="s">
-        <v>19</v>
-      </c>
-      <c r="L47" t="s">
-        <v>179</v>
-      </c>
-      <c r="M47" t="s">
-        <v>20</v>
-      </c>
-      <c r="N47" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>174</v>
-      </c>
-      <c r="B48" t="s">
-        <v>116</v>
-      </c>
-      <c r="C48" t="s">
-        <v>309</v>
-      </c>
-      <c r="D48" t="s">
-        <v>126</v>
-      </c>
-      <c r="E48" t="s">
-        <v>127</v>
-      </c>
-      <c r="F48" t="s">
-        <v>128</v>
-      </c>
-      <c r="G48" t="s">
-        <v>15</v>
-      </c>
-      <c r="H48" t="s">
-        <v>125</v>
-      </c>
-      <c r="I48" t="s">
-        <v>17</v>
-      </c>
-      <c r="J48" t="s">
-        <v>18</v>
-      </c>
-      <c r="K48" t="s">
-        <v>19</v>
-      </c>
-      <c r="L48" t="s">
-        <v>179</v>
-      </c>
-      <c r="M48" t="s">
-        <v>20</v>
-      </c>
-      <c r="N48" t="s">
-        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -3839,88 +3238,68 @@
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>149</v>
+        <v>48</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>150</v>
+        <v>49</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>151</v>
+        <v>50</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>152</v>
+        <v>51</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>153</v>
+        <v>52</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>154</v>
+        <v>53</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>155</v>
+        <v>54</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>156</v>
+        <v>55</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>157</v>
+        <v>56</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>158</v>
+        <v>57</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>159</v>
+        <v>58</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>160</v>
+        <v>59</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>161</v>
+        <v>60</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>162</v>
+        <v>61</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>163</v>
+        <v>62</v>
       </c>
       <c r="P1" s="4" t="s">
-        <v>164</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="18" t="s">
-        <v>165</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="C2" s="7">
-        <v>46218</v>
-      </c>
-      <c r="D2" s="6">
-        <v>85435</v>
-      </c>
-      <c r="E2" s="6">
-        <v>2</v>
-      </c>
-      <c r="F2" s="6">
-        <v>6878176600</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="H2" s="6">
-        <v>1160</v>
-      </c>
-      <c r="I2" s="6">
-        <v>29</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="K2" s="6" t="s">
-        <v>169</v>
-      </c>
+      <c r="A2" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
       <c r="L2" s="6"/>
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
@@ -3928,37 +3307,17 @@
       <c r="P2" s="8"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="18"/>
-      <c r="B3" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="C3" s="7">
-        <v>46218</v>
-      </c>
-      <c r="D3" s="6">
-        <v>85486</v>
-      </c>
-      <c r="E3" s="6">
-        <v>3</v>
-      </c>
-      <c r="F3" s="6">
-        <v>6878107316</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="H3" s="6">
-        <v>991</v>
-      </c>
-      <c r="I3" s="6">
-        <v>25</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="K3" s="6" t="s">
-        <v>169</v>
-      </c>
+      <c r="A3" s="20"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
       <c r="L3" s="6"/>
       <c r="M3" s="6"/>
       <c r="N3" s="6"/>
@@ -3966,19 +3325,11 @@
       <c r="P3" s="8"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="18"/>
-      <c r="B4" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="C4" s="7">
-        <v>46218</v>
-      </c>
-      <c r="D4" s="6">
-        <v>85434</v>
-      </c>
-      <c r="E4" s="6">
-        <v>3</v>
-      </c>
+      <c r="A4" s="20"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
       <c r="H4" s="6"/>
@@ -3992,19 +3343,11 @@
       <c r="P4" s="8"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="18"/>
-      <c r="B5" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="C5" s="7">
-        <v>46218</v>
-      </c>
-      <c r="D5" s="6">
-        <v>85358</v>
-      </c>
-      <c r="E5" s="6">
-        <v>3</v>
-      </c>
+      <c r="A5" s="20"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>
@@ -4018,19 +3361,11 @@
       <c r="P5" s="8"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" s="18"/>
-      <c r="B6" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="C6" s="7">
-        <v>46218</v>
-      </c>
-      <c r="D6" s="6">
-        <v>85437</v>
-      </c>
-      <c r="E6" s="6">
-        <v>4</v>
-      </c>
+      <c r="A6" s="20"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
       <c r="F6" s="6"/>
       <c r="G6" s="6"/>
       <c r="H6" s="6"/>
@@ -4044,7 +3379,7 @@
       <c r="P6" s="8"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" s="18"/>
+      <c r="A7" s="20"/>
       <c r="B7" s="9"/>
       <c r="C7" s="10"/>
       <c r="D7" s="9"/>
@@ -4062,39 +3397,19 @@
       <c r="P7" s="11"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" s="18" t="s">
-        <v>171</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="C8" s="12">
-        <v>46218</v>
-      </c>
-      <c r="D8" s="6">
-        <v>85438</v>
-      </c>
-      <c r="E8" s="6">
-        <v>1</v>
-      </c>
-      <c r="F8" s="6">
-        <v>6878176930</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="H8" s="6">
-        <v>953</v>
-      </c>
-      <c r="I8" s="6">
-        <v>25</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="K8" s="6" t="s">
-        <v>172</v>
-      </c>
+      <c r="A8" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="B8" s="6"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
       <c r="L8" s="6"/>
       <c r="M8" s="6"/>
       <c r="N8" s="6"/>
@@ -4102,7 +3417,7 @@
       <c r="P8" s="8"/>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" s="18"/>
+      <c r="A9" s="20"/>
       <c r="B9" s="6"/>
       <c r="C9" s="12"/>
       <c r="D9" s="6"/>
@@ -4120,7 +3435,7 @@
       <c r="P9" s="8"/>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" s="18"/>
+      <c r="A10" s="20"/>
       <c r="B10" s="9"/>
       <c r="C10" s="13"/>
       <c r="D10" s="9"/>
@@ -4139,16 +3454,36 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
+      <c r="B11" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="C11" s="19">
+        <v>46226</v>
+      </c>
+      <c r="D11" s="18">
+        <v>87517</v>
+      </c>
+      <c r="E11" s="18">
+        <v>1</v>
+      </c>
+      <c r="F11" s="18">
+        <v>6878304268</v>
+      </c>
+      <c r="G11" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="H11" s="18">
+        <v>341</v>
+      </c>
+      <c r="I11" s="18">
+        <v>9</v>
+      </c>
+      <c r="J11" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="K11" s="18" t="s">
+        <v>68</v>
+      </c>
       <c r="L11" s="6"/>
       <c r="M11" s="6"/>
       <c r="N11" s="6"/>
@@ -4156,19 +3491,39 @@
       <c r="P11" s="8"/>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" s="18" t="s">
-        <v>173</v>
-      </c>
-      <c r="B12" s="6"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
+      <c r="A12" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12" s="12">
+        <v>46226</v>
+      </c>
+      <c r="D12" s="6">
+        <v>87518</v>
+      </c>
+      <c r="E12" s="6">
+        <v>1</v>
+      </c>
+      <c r="F12" s="6">
+        <v>6878304269</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="H12" s="6">
+        <v>823</v>
+      </c>
+      <c r="I12" s="6">
+        <v>21</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>68</v>
+      </c>
       <c r="L12" s="6"/>
       <c r="M12" s="6"/>
       <c r="N12" s="6"/>
@@ -4176,17 +3531,37 @@
       <c r="P12" s="8"/>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" s="18"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="6"/>
+      <c r="A13" s="20"/>
+      <c r="B13" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C13" s="12">
+        <v>46226</v>
+      </c>
+      <c r="D13" s="6">
+        <v>87519</v>
+      </c>
+      <c r="E13" s="6">
+        <v>2</v>
+      </c>
+      <c r="F13" s="6">
+        <v>6878309020</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="H13" s="6">
+        <v>1008</v>
+      </c>
+      <c r="I13" s="6">
+        <v>26</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="K13" s="6" t="s">
+        <v>228</v>
+      </c>
       <c r="L13" s="6"/>
       <c r="M13" s="6"/>
       <c r="N13" s="6"/>
@@ -4194,17 +3569,37 @@
       <c r="P13" s="8"/>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" s="18"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
+      <c r="A14" s="20"/>
+      <c r="B14" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" s="12">
+        <v>46226</v>
+      </c>
+      <c r="D14" s="6">
+        <v>87515</v>
+      </c>
+      <c r="E14" s="6">
+        <v>2</v>
+      </c>
+      <c r="F14" s="6">
+        <v>6878304266</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="I14" s="6">
+        <v>2</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="K14" s="6" t="s">
+        <v>68</v>
+      </c>
       <c r="L14" s="6"/>
       <c r="M14" s="6"/>
       <c r="N14" s="6"/>
@@ -4212,17 +3607,37 @@
       <c r="P14" s="8"/>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" s="18"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-      <c r="K15" s="6"/>
+      <c r="A15" s="20"/>
+      <c r="B15" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15" s="12">
+        <v>46226</v>
+      </c>
+      <c r="D15" s="6">
+        <v>87516</v>
+      </c>
+      <c r="E15" s="6">
+        <v>2</v>
+      </c>
+      <c r="F15" s="6">
+        <v>6878304267</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="I15" s="6">
+        <v>2</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="K15" s="6" t="s">
+        <v>68</v>
+      </c>
       <c r="L15" s="6"/>
       <c r="M15" s="6"/>
       <c r="N15" s="6"/>
@@ -4230,17 +3645,37 @@
       <c r="P15" s="8"/>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A16" s="18"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
-      <c r="K16" s="6"/>
+      <c r="A16" s="20"/>
+      <c r="B16" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C16" s="12">
+        <v>46226</v>
+      </c>
+      <c r="D16" s="6">
+        <v>87520</v>
+      </c>
+      <c r="E16" s="6">
+        <v>3</v>
+      </c>
+      <c r="F16" s="6">
+        <v>6878309021</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="H16" s="6">
+        <v>1158</v>
+      </c>
+      <c r="I16" s="6">
+        <v>29</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="K16" s="6" t="s">
+        <v>68</v>
+      </c>
       <c r="L16" s="6"/>
       <c r="M16" s="6"/>
       <c r="N16" s="6"/>
@@ -4248,7 +3683,7 @@
       <c r="P16" s="8"/>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A17" s="18"/>
+      <c r="A17" s="20"/>
       <c r="B17" s="6"/>
       <c r="C17" s="7"/>
       <c r="D17" s="6"/>
@@ -4266,7 +3701,7 @@
       <c r="P17" s="8"/>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18" s="18"/>
+      <c r="A18" s="20"/>
       <c r="B18" s="9"/>
       <c r="C18" s="10"/>
       <c r="D18" s="9"/>
@@ -4289,72 +3724,80 @@
     <mergeCell ref="A8:A10"/>
     <mergeCell ref="A12:A18"/>
   </mergeCells>
-  <conditionalFormatting sqref="G2:H18 M2:M18">
-    <cfRule type="cellIs" dxfId="19" priority="8" operator="equal">
+  <conditionalFormatting sqref="G2:H18">
+    <cfRule type="cellIs" dxfId="21" priority="7" operator="equal">
       <formula>"Sim"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="8" operator="equal">
       <formula>"Não"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J18">
-    <cfRule type="cellIs" dxfId="17" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="5" operator="equal">
       <formula>"Não"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="6" operator="equal">
       <formula>"SIm"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J6">
-    <cfRule type="cellIs" dxfId="15" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="18" operator="equal">
       <formula>"Sim"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K18">
-    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
       <formula>"Aberto"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="2" operator="equal">
       <formula>"Abrir"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="3" operator="equal">
       <formula>"Respondido"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="4" operator="equal">
       <formula>"NA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L18">
-    <cfRule type="cellIs" dxfId="10" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="19" operator="equal">
       <formula>8</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="20" operator="equal">
       <formula>7</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="21" operator="equal">
       <formula>5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="22" operator="equal">
       <formula>4</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="23" operator="equal">
       <formula>2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="24" operator="equal">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="25" operator="equal">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="26" operator="equal">
       <formula>9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="27" operator="equal">
       <formula>6</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="M2:M18">
+    <cfRule type="cellIs" dxfId="3" priority="16" operator="equal">
+      <formula>"Sim"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="17" operator="equal">
+      <formula>"Não"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="P2:P18">
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="11" operator="equal">
       <formula>"Email enviado"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4370,10 +3813,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>138</v>
+        <v>37</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>139</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -4381,7 +3824,7 @@
         <v>10053057</v>
       </c>
       <c r="B2" t="s">
-        <v>142</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -4389,7 +3832,7 @@
         <v>10158803</v>
       </c>
       <c r="B3" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -4397,7 +3840,7 @@
         <v>10165171</v>
       </c>
       <c r="B4" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -4405,7 +3848,7 @@
         <v>10186344</v>
       </c>
       <c r="B5" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -4413,7 +3856,7 @@
         <v>10198819</v>
       </c>
       <c r="B6" t="s">
-        <v>144</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -4421,7 +3864,7 @@
         <v>10199089</v>
       </c>
       <c r="B7" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -4429,7 +3872,7 @@
         <v>10208003</v>
       </c>
       <c r="B8" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -4437,7 +3880,7 @@
         <v>10208004</v>
       </c>
       <c r="B9" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -4445,7 +3888,7 @@
         <v>10208005</v>
       </c>
       <c r="B10" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -4453,7 +3896,7 @@
         <v>10208167</v>
       </c>
       <c r="B11" t="s">
-        <v>141</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -4461,7 +3904,7 @@
         <v>10215610</v>
       </c>
       <c r="B12" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -4469,7 +3912,7 @@
         <v>10215641</v>
       </c>
       <c r="B13" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -4477,7 +3920,7 @@
         <v>10223108</v>
       </c>
       <c r="B14" t="s">
-        <v>144</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -4485,7 +3928,7 @@
         <v>10223112</v>
       </c>
       <c r="B15" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -4493,7 +3936,7 @@
         <v>10223123</v>
       </c>
       <c r="B16" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -4501,7 +3944,7 @@
         <v>10223131</v>
       </c>
       <c r="B17" t="s">
-        <v>144</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -4509,7 +3952,7 @@
         <v>10223132</v>
       </c>
       <c r="B18" t="s">
-        <v>144</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -4517,7 +3960,7 @@
         <v>10223435</v>
       </c>
       <c r="B19" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -4525,7 +3968,7 @@
         <v>10223657</v>
       </c>
       <c r="B20" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -4533,7 +3976,7 @@
         <v>10224283</v>
       </c>
       <c r="B21" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -4541,7 +3984,7 @@
         <v>10224293</v>
       </c>
       <c r="B22" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -4549,7 +3992,7 @@
         <v>10224317</v>
       </c>
       <c r="B23" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -4557,7 +4000,7 @@
         <v>10224317</v>
       </c>
       <c r="B24" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -4565,7 +4008,7 @@
         <v>10224318</v>
       </c>
       <c r="B25" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -4573,7 +4016,7 @@
         <v>10224318</v>
       </c>
       <c r="B26" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -4581,7 +4024,7 @@
         <v>10224332</v>
       </c>
       <c r="B27" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -4589,7 +4032,7 @@
         <v>10224332</v>
       </c>
       <c r="B28" t="s">
-        <v>144</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -4597,7 +4040,7 @@
         <v>10224333</v>
       </c>
       <c r="B29" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -4605,7 +4048,7 @@
         <v>10224333</v>
       </c>
       <c r="B30" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -4613,7 +4056,7 @@
         <v>10225180</v>
       </c>
       <c r="B31" t="s">
-        <v>144</v>
+        <v>43</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -4621,7 +4064,7 @@
         <v>10226339</v>
       </c>
       <c r="B32" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -4629,7 +4072,7 @@
         <v>10226359</v>
       </c>
       <c r="B33" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -4637,7 +4080,7 @@
         <v>10226361</v>
       </c>
       <c r="B34" t="s">
-        <v>144</v>
+        <v>43</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -4645,7 +4088,7 @@
         <v>10226362</v>
       </c>
       <c r="B35" t="s">
-        <v>144</v>
+        <v>43</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -4653,7 +4096,7 @@
         <v>10226362</v>
       </c>
       <c r="B36" t="s">
-        <v>144</v>
+        <v>43</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -4661,7 +4104,7 @@
         <v>10226363</v>
       </c>
       <c r="B37" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -4669,7 +4112,7 @@
         <v>10226367</v>
       </c>
       <c r="B38" t="s">
-        <v>143</v>
+        <v>42</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -4677,7 +4120,7 @@
         <v>10226368</v>
       </c>
       <c r="B39" t="s">
-        <v>143</v>
+        <v>42</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -4685,7 +4128,7 @@
         <v>10226371</v>
       </c>
       <c r="B40" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -4693,7 +4136,7 @@
         <v>10226372</v>
       </c>
       <c r="B41" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -4701,7 +4144,7 @@
         <v>10226373</v>
       </c>
       <c r="B42" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -4709,7 +4152,7 @@
         <v>10226374</v>
       </c>
       <c r="B43" t="s">
-        <v>143</v>
+        <v>42</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -4717,7 +4160,7 @@
         <v>10226380</v>
       </c>
       <c r="B44" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -4725,7 +4168,7 @@
         <v>10226385</v>
       </c>
       <c r="B45" t="s">
-        <v>144</v>
+        <v>43</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -4733,7 +4176,7 @@
         <v>10226386</v>
       </c>
       <c r="B46" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -4741,7 +4184,7 @@
         <v>10226387</v>
       </c>
       <c r="B47" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -4749,7 +4192,7 @@
         <v>10226388</v>
       </c>
       <c r="B48" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -4757,7 +4200,7 @@
         <v>10226392</v>
       </c>
       <c r="B49" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -4765,7 +4208,7 @@
         <v>10226396</v>
       </c>
       <c r="B50" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -4773,7 +4216,7 @@
         <v>10226397</v>
       </c>
       <c r="B51" t="s">
-        <v>144</v>
+        <v>43</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -4781,7 +4224,7 @@
         <v>10226398</v>
       </c>
       <c r="B52" t="s">
-        <v>144</v>
+        <v>43</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -4789,7 +4232,7 @@
         <v>10226399</v>
       </c>
       <c r="B53" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -4797,7 +4240,7 @@
         <v>10226400</v>
       </c>
       <c r="B54" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -4805,7 +4248,7 @@
         <v>10226401</v>
       </c>
       <c r="B55" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -4813,7 +4256,7 @@
         <v>10226402</v>
       </c>
       <c r="B56" t="s">
-        <v>144</v>
+        <v>43</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -4821,7 +4264,7 @@
         <v>10226403</v>
       </c>
       <c r="B57" t="s">
-        <v>144</v>
+        <v>43</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -4829,7 +4272,7 @@
         <v>10226404</v>
       </c>
       <c r="B58" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -4837,7 +4280,7 @@
         <v>10226405</v>
       </c>
       <c r="B59" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
@@ -4845,7 +4288,7 @@
         <v>10226406</v>
       </c>
       <c r="B60" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
@@ -4853,7 +4296,7 @@
         <v>10226407</v>
       </c>
       <c r="B61" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
@@ -4861,7 +4304,7 @@
         <v>10226409</v>
       </c>
       <c r="B62" t="s">
-        <v>144</v>
+        <v>43</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -4869,7 +4312,7 @@
         <v>10226410</v>
       </c>
       <c r="B63" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -4877,7 +4320,7 @@
         <v>10226412</v>
       </c>
       <c r="B64" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
@@ -4885,7 +4328,7 @@
         <v>10226413</v>
       </c>
       <c r="B65" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
@@ -4893,7 +4336,7 @@
         <v>10226415</v>
       </c>
       <c r="B66" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
@@ -4901,7 +4344,7 @@
         <v>10226417</v>
       </c>
       <c r="B67" t="s">
-        <v>144</v>
+        <v>43</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
@@ -4909,7 +4352,7 @@
         <v>10226418</v>
       </c>
       <c r="B68" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
@@ -4917,7 +4360,7 @@
         <v>10226420</v>
       </c>
       <c r="B69" t="s">
-        <v>144</v>
+        <v>43</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -4925,7 +4368,7 @@
         <v>10226421</v>
       </c>
       <c r="B70" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
@@ -4933,7 +4376,7 @@
         <v>10226422</v>
       </c>
       <c r="B71" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
@@ -4941,7 +4384,7 @@
         <v>10226425</v>
       </c>
       <c r="B72" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
@@ -4949,7 +4392,7 @@
         <v>10226427</v>
       </c>
       <c r="B73" t="s">
-        <v>144</v>
+        <v>43</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
@@ -4957,7 +4400,7 @@
         <v>10226429</v>
       </c>
       <c r="B74" t="s">
-        <v>144</v>
+        <v>43</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
@@ -4965,7 +4408,7 @@
         <v>10226430</v>
       </c>
       <c r="B75" t="s">
-        <v>144</v>
+        <v>43</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
@@ -4973,7 +4416,7 @@
         <v>10226431</v>
       </c>
       <c r="B76" t="s">
-        <v>144</v>
+        <v>43</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
@@ -4981,7 +4424,7 @@
         <v>10226432</v>
       </c>
       <c r="B77" t="s">
-        <v>144</v>
+        <v>43</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
@@ -4989,7 +4432,7 @@
         <v>10226435</v>
       </c>
       <c r="B78" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
@@ -4997,7 +4440,7 @@
         <v>10226437</v>
       </c>
       <c r="B79" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
@@ -5005,7 +4448,7 @@
         <v>10226438</v>
       </c>
       <c r="B80" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
@@ -5013,7 +4456,7 @@
         <v>10226439</v>
       </c>
       <c r="B81" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
@@ -5021,7 +4464,7 @@
         <v>10226441</v>
       </c>
       <c r="B82" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
@@ -5029,7 +4472,7 @@
         <v>10226442</v>
       </c>
       <c r="B83" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
@@ -5037,7 +4480,7 @@
         <v>10226444</v>
       </c>
       <c r="B84" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
@@ -5045,7 +4488,7 @@
         <v>10226445</v>
       </c>
       <c r="B85" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
@@ -5053,7 +4496,7 @@
         <v>10226446</v>
       </c>
       <c r="B86" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
@@ -5061,7 +4504,7 @@
         <v>10226447</v>
       </c>
       <c r="B87" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
@@ -5069,7 +4512,7 @@
         <v>10226452</v>
       </c>
       <c r="B88" t="s">
-        <v>141</v>
+        <v>40</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
@@ -5077,7 +4520,7 @@
         <v>10226453</v>
       </c>
       <c r="B89" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
@@ -5085,7 +4528,7 @@
         <v>10226454</v>
       </c>
       <c r="B90" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
@@ -5093,7 +4536,7 @@
         <v>10226455</v>
       </c>
       <c r="B91" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
@@ -5101,7 +4544,7 @@
         <v>10226463</v>
       </c>
       <c r="B92" t="s">
-        <v>144</v>
+        <v>43</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
@@ -5109,7 +4552,7 @@
         <v>10226618</v>
       </c>
       <c r="B93" t="s">
-        <v>144</v>
+        <v>43</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
@@ -5117,7 +4560,7 @@
         <v>10226781</v>
       </c>
       <c r="B94" t="s">
-        <v>144</v>
+        <v>43</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
@@ -5125,7 +4568,7 @@
         <v>10227069</v>
       </c>
       <c r="B95" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
@@ -5133,7 +4576,7 @@
         <v>10227309</v>
       </c>
       <c r="B96" t="s">
-        <v>144</v>
+        <v>43</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
@@ -5141,7 +4584,7 @@
         <v>10227310</v>
       </c>
       <c r="B97" t="s">
-        <v>144</v>
+        <v>43</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
@@ -5149,7 +4592,7 @@
         <v>10227896</v>
       </c>
       <c r="B98" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
@@ -5157,7 +4600,7 @@
         <v>10230675</v>
       </c>
       <c r="B99" t="s">
-        <v>142</v>
+        <v>41</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
@@ -5165,7 +4608,7 @@
         <v>10231475</v>
       </c>
       <c r="B100" t="s">
-        <v>144</v>
+        <v>43</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
@@ -5173,7 +4616,7 @@
         <v>10231484</v>
       </c>
       <c r="B101" t="s">
-        <v>144</v>
+        <v>43</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
@@ -5181,7 +4624,7 @@
         <v>10236617</v>
       </c>
       <c r="B102" t="s">
-        <v>144</v>
+        <v>43</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
@@ -5189,7 +4632,7 @@
         <v>10236618</v>
       </c>
       <c r="B103" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
@@ -5197,7 +4640,7 @@
         <v>10236662</v>
       </c>
       <c r="B104" t="s">
-        <v>144</v>
+        <v>43</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
@@ -5205,7 +4648,7 @@
         <v>10236672</v>
       </c>
       <c r="B105" t="s">
-        <v>144</v>
+        <v>43</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
@@ -5213,7 +4656,7 @@
         <v>10238737</v>
       </c>
       <c r="B106" t="s">
-        <v>143</v>
+        <v>42</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
@@ -5221,7 +4664,7 @@
         <v>10242280</v>
       </c>
       <c r="B107" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
@@ -5229,7 +4672,7 @@
         <v>10242291</v>
       </c>
       <c r="B108" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
@@ -5237,7 +4680,7 @@
         <v>10242293</v>
       </c>
       <c r="B109" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
@@ -5245,7 +4688,7 @@
         <v>10247603</v>
       </c>
       <c r="B110" t="s">
-        <v>143</v>
+        <v>42</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
@@ -5253,7 +4696,7 @@
         <v>10247604</v>
       </c>
       <c r="B111" t="s">
-        <v>143</v>
+        <v>42</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
@@ -5261,7 +4704,7 @@
         <v>10247605</v>
       </c>
       <c r="B112" t="s">
-        <v>143</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -5294,21 +4737,21 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
-        <v>147</v>
+        <v>46</v>
       </c>
       <c r="B1" s="15" t="str">
         <f>'Colar Pedido'!A2</f>
-        <v>6878107316</v>
+        <v>6878309021</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>148</v>
+        <v>47</v>
       </c>
       <c r="D1" s="15">
         <f>_xlfn.XLOOKUP(VALUE(B1),'Colar Acompanhamento'!F:F,'Colar Acompanhamento'!E:E,"")</f>
         <v>3</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>149</v>
+        <v>48</v>
       </c>
       <c r="F1" s="15">
         <f>_xlfn.XLOOKUP(VALUE(B1),'Colar Acompanhamento'!F:F,'Colar Acompanhamento'!A:A,"")</f>
@@ -5332,27 +4775,27 @@
         <v>8</v>
       </c>
       <c r="D3" s="17" t="s">
-        <v>145</v>
+        <v>44</v>
       </c>
       <c r="E3" s="17" t="s">
         <v>2</v>
       </c>
       <c r="F3" s="17" t="s">
-        <v>146</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!E2), "", 'Colar Pedido'!E2)</f>
-        <v>FR.01.02.01.04</v>
+        <v>FR.01.01.01.02</v>
       </c>
       <c r="B4" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!H2),"",'Colar Pedido'!H2)</f>
-        <v>10226380</v>
+        <v>10226421</v>
       </c>
       <c r="C4" s="16">
         <f>IF(ISBLANK('Colar Pedido'!I2),"",VALUE('Colar Pedido'!I2))</f>
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="D4" s="16" t="str">
         <f>IF(Imprimir!B4="", "", _xlfn.XLOOKUP(VALUE(Imprimir!B4),DB!A:A,DB!B:B,""))</f>
@@ -5360,39 +4803,39 @@
       </c>
       <c r="E4" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!C2),"",'Colar Pedido'!C2)</f>
-        <v>0000118134</v>
+        <v>0000125351</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!E3), "", 'Colar Pedido'!E3)</f>
-        <v>FR.01.02.01.03</v>
+        <v>BLE048</v>
       </c>
       <c r="B5" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!H3),"",'Colar Pedido'!H3)</f>
-        <v>10226386</v>
+        <v>10242292</v>
       </c>
       <c r="C5" s="16">
         <f>IF(ISBLANK('Colar Pedido'!I3),"",VALUE('Colar Pedido'!I3))</f>
-        <v>20</v>
+        <v>400</v>
       </c>
       <c r="D5" s="16" t="str">
         <f>IF(Imprimir!B5="", "", _xlfn.XLOOKUP(VALUE(Imprimir!B5),DB!A:A,DB!B:B,""))</f>
-        <v>BOX</v>
+        <v/>
       </c>
       <c r="E5" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!C3),"",'Colar Pedido'!C3)</f>
-        <v>0000118130</v>
+        <v>0000125361</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!E4), "", 'Colar Pedido'!E4)</f>
-        <v>BLH057</v>
+        <v>BLE066</v>
       </c>
       <c r="B6" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!H4),"",'Colar Pedido'!H4)</f>
-        <v>10215641</v>
+        <v>10242292</v>
       </c>
       <c r="C6" s="16">
         <f>IF(ISBLANK('Colar Pedido'!I4),"",VALUE('Colar Pedido'!I4))</f>
@@ -5400,21 +4843,21 @@
       </c>
       <c r="D6" s="16" t="str">
         <f>IF(Imprimir!B6="", "", _xlfn.XLOOKUP(VALUE(Imprimir!B6),DB!A:A,DB!B:B,""))</f>
-        <v>BOX</v>
+        <v/>
       </c>
       <c r="E6" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!C4),"",'Colar Pedido'!C4)</f>
-        <v>0000118123</v>
+        <v>0000125477</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!E5), "", 'Colar Pedido'!E5)</f>
-        <v>BLH057</v>
+        <v>BLE069</v>
       </c>
       <c r="B7" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!H5),"",'Colar Pedido'!H5)</f>
-        <v>10215641</v>
+        <v>10242292</v>
       </c>
       <c r="C7" s="16">
         <f>IF(ISBLANK('Colar Pedido'!I5),"",VALUE('Colar Pedido'!I5))</f>
@@ -5422,21 +4865,21 @@
       </c>
       <c r="D7" s="16" t="str">
         <f>IF(Imprimir!B7="", "", _xlfn.XLOOKUP(VALUE(Imprimir!B7),DB!A:A,DB!B:B,""))</f>
-        <v>BOX</v>
+        <v/>
       </c>
       <c r="E7" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!C5),"",'Colar Pedido'!C5)</f>
-        <v>0000118124</v>
+        <v>0000125478</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!E6), "", 'Colar Pedido'!E6)</f>
-        <v>BLH079</v>
+        <v>BLF051</v>
       </c>
       <c r="B8" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!H6),"",'Colar Pedido'!H6)</f>
-        <v>10215641</v>
+        <v>10242292</v>
       </c>
       <c r="C8" s="16">
         <f>IF(ISBLANK('Colar Pedido'!I6),"",VALUE('Colar Pedido'!I6))</f>
@@ -5444,21 +4887,21 @@
       </c>
       <c r="D8" s="16" t="str">
         <f>IF(Imprimir!B8="", "", _xlfn.XLOOKUP(VALUE(Imprimir!B8),DB!A:A,DB!B:B,""))</f>
-        <v>BOX</v>
+        <v/>
       </c>
       <c r="E8" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!C6),"",'Colar Pedido'!C6)</f>
-        <v>0000118125</v>
+        <v>0000125479</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!E7), "", 'Colar Pedido'!E7)</f>
-        <v>BLG087</v>
+        <v>BLF054</v>
       </c>
       <c r="B9" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!H7),"",'Colar Pedido'!H7)</f>
-        <v>10223435</v>
+        <v>10242292</v>
       </c>
       <c r="C9" s="16">
         <f>IF(ISBLANK('Colar Pedido'!I7),"",VALUE('Colar Pedido'!I7))</f>
@@ -5466,43 +4909,43 @@
       </c>
       <c r="D9" s="16" t="str">
         <f>IF(Imprimir!B9="", "", _xlfn.XLOOKUP(VALUE(Imprimir!B9),DB!A:A,DB!B:B,""))</f>
-        <v>BOX</v>
+        <v/>
       </c>
       <c r="E9" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!C7),"",'Colar Pedido'!C7)</f>
-        <v>0000118126</v>
+        <v>0000125480</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!E8), "", 'Colar Pedido'!E8)</f>
-        <v>BLH077</v>
+        <v>BLF054</v>
       </c>
       <c r="B10" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!H8),"",'Colar Pedido'!H8)</f>
-        <v>10223435</v>
+        <v>10242292</v>
       </c>
       <c r="C10" s="16">
         <f>IF(ISBLANK('Colar Pedido'!I8),"",VALUE('Colar Pedido'!I8))</f>
-        <v>30</v>
+        <v>400</v>
       </c>
       <c r="D10" s="16" t="str">
         <f>IF(Imprimir!B10="", "", _xlfn.XLOOKUP(VALUE(Imprimir!B10),DB!A:A,DB!B:B,""))</f>
-        <v>BOX</v>
+        <v/>
       </c>
       <c r="E10" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!C8),"",'Colar Pedido'!C8)</f>
-        <v>0000118227</v>
+        <v>0000125481</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!E9), "", 'Colar Pedido'!E9)</f>
-        <v>BLG003</v>
+        <v>BLF056</v>
       </c>
       <c r="B11" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!H9),"",'Colar Pedido'!H9)</f>
-        <v>10223108</v>
+        <v>10242292</v>
       </c>
       <c r="C11" s="16">
         <f>IF(ISBLANK('Colar Pedido'!I9),"",VALUE('Colar Pedido'!I9))</f>
@@ -5510,21 +4953,21 @@
       </c>
       <c r="D11" s="16" t="str">
         <f>IF(Imprimir!B11="", "", _xlfn.XLOOKUP(VALUE(Imprimir!B11),DB!A:A,DB!B:B,""))</f>
-        <v>SLIVE</v>
+        <v/>
       </c>
       <c r="E11" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!C9),"",'Colar Pedido'!C9)</f>
-        <v>0000118228</v>
+        <v>0000125482</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!E10), "", 'Colar Pedido'!E10)</f>
-        <v>BLH058</v>
+        <v>BLF056</v>
       </c>
       <c r="B12" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!H10),"",'Colar Pedido'!H10)</f>
-        <v>10223108</v>
+        <v>10242292</v>
       </c>
       <c r="C12" s="16">
         <f>IF(ISBLANK('Colar Pedido'!I10),"",VALUE('Colar Pedido'!I10))</f>
@@ -5532,197 +4975,197 @@
       </c>
       <c r="D12" s="16" t="str">
         <f>IF(Imprimir!B12="", "", _xlfn.XLOOKUP(VALUE(Imprimir!B12),DB!A:A,DB!B:B,""))</f>
-        <v>SLIVE</v>
+        <v/>
       </c>
       <c r="E12" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!C10),"",'Colar Pedido'!C10)</f>
-        <v>0000118229</v>
+        <v>0000125483</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!E11), "", 'Colar Pedido'!E11)</f>
-        <v>BLG003</v>
+        <v>BLF070</v>
       </c>
       <c r="B13" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!H11),"",'Colar Pedido'!H11)</f>
-        <v>10223108</v>
+        <v>10242292</v>
       </c>
       <c r="C13" s="16">
         <f>IF(ISBLANK('Colar Pedido'!I11),"",VALUE('Colar Pedido'!I11))</f>
-        <v>110</v>
+        <v>400</v>
       </c>
       <c r="D13" s="16" t="str">
         <f>IF(Imprimir!B13="", "", _xlfn.XLOOKUP(VALUE(Imprimir!B13),DB!A:A,DB!B:B,""))</f>
-        <v>SLIVE</v>
+        <v/>
       </c>
       <c r="E13" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!C11),"",'Colar Pedido'!C11)</f>
-        <v>0000118230</v>
+        <v>0000125484</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!E12), "", 'Colar Pedido'!E12)</f>
-        <v>BLE006</v>
+        <v>BLF072</v>
       </c>
       <c r="B14" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!H12),"",'Colar Pedido'!H12)</f>
-        <v>10226385</v>
+        <v>10242292</v>
       </c>
       <c r="C14" s="16">
         <f>IF(ISBLANK('Colar Pedido'!I12),"",VALUE('Colar Pedido'!I12))</f>
-        <v>10</v>
+        <v>400</v>
       </c>
       <c r="D14" s="16" t="str">
         <f>IF(Imprimir!B14="", "", _xlfn.XLOOKUP(VALUE(Imprimir!B14),DB!A:A,DB!B:B,""))</f>
-        <v>SLIVE</v>
+        <v/>
       </c>
       <c r="E14" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!C12),"",'Colar Pedido'!C12)</f>
-        <v>0000118231</v>
+        <v>0000125485</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!E13), "", 'Colar Pedido'!E13)</f>
-        <v>BLF043</v>
+        <v>BLF072</v>
       </c>
       <c r="B15" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!H13),"",'Colar Pedido'!H13)</f>
-        <v>10226361</v>
+        <v>10242292</v>
       </c>
       <c r="C15" s="16">
         <f>IF(ISBLANK('Colar Pedido'!I13),"",VALUE('Colar Pedido'!I13))</f>
-        <v>40</v>
+        <v>400</v>
       </c>
       <c r="D15" s="16" t="str">
         <f>IF(Imprimir!B15="", "", _xlfn.XLOOKUP(VALUE(Imprimir!B15),DB!A:A,DB!B:B,""))</f>
-        <v>SLIVE</v>
+        <v/>
       </c>
       <c r="E15" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!C13),"",'Colar Pedido'!C13)</f>
-        <v>0000118232</v>
+        <v>0000125486</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!E14), "", 'Colar Pedido'!E14)</f>
-        <v>BLF083</v>
+        <v>BLF088</v>
       </c>
       <c r="B16" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!H14),"",'Colar Pedido'!H14)</f>
-        <v>10224293</v>
+        <v>10242292</v>
       </c>
       <c r="C16" s="16">
         <f>IF(ISBLANK('Colar Pedido'!I14),"",VALUE('Colar Pedido'!I14))</f>
-        <v>120</v>
+        <v>400</v>
       </c>
       <c r="D16" s="16" t="str">
         <f>IF(Imprimir!B16="", "", _xlfn.XLOOKUP(VALUE(Imprimir!B16),DB!A:A,DB!B:B,""))</f>
-        <v>BOX</v>
+        <v/>
       </c>
       <c r="E16" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!C14),"",'Colar Pedido'!C14)</f>
-        <v>0000118233</v>
+        <v>0000125487</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!E15), "", 'Colar Pedido'!E15)</f>
-        <v>BLF089</v>
+        <v>BLF090</v>
       </c>
       <c r="B17" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!H15),"",'Colar Pedido'!H15)</f>
-        <v>10224293</v>
+        <v>10242292</v>
       </c>
       <c r="C17" s="16">
         <f>IF(ISBLANK('Colar Pedido'!I15),"",VALUE('Colar Pedido'!I15))</f>
-        <v>50</v>
+        <v>400</v>
       </c>
       <c r="D17" s="16" t="str">
         <f>IF(Imprimir!B17="", "", _xlfn.XLOOKUP(VALUE(Imprimir!B17),DB!A:A,DB!B:B,""))</f>
-        <v>BOX</v>
+        <v/>
       </c>
       <c r="E17" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!C15),"",'Colar Pedido'!C15)</f>
-        <v>0000118234</v>
+        <v>0000125488</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!E16), "", 'Colar Pedido'!E16)</f>
-        <v>BLH065</v>
+        <v>BLF090</v>
       </c>
       <c r="B18" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!H16),"",'Colar Pedido'!H16)</f>
-        <v>10223657</v>
+        <v>10242292</v>
       </c>
       <c r="C18" s="16">
         <f>IF(ISBLANK('Colar Pedido'!I16),"",VALUE('Colar Pedido'!I16))</f>
-        <v>170</v>
+        <v>400</v>
       </c>
       <c r="D18" s="16" t="str">
         <f>IF(Imprimir!B18="", "", _xlfn.XLOOKUP(VALUE(Imprimir!B18),DB!A:A,DB!B:B,""))</f>
-        <v>BOX</v>
+        <v/>
       </c>
       <c r="E18" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!C16),"",'Colar Pedido'!C16)</f>
-        <v>0000118235</v>
+        <v>0000125489</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!E17), "", 'Colar Pedido'!E17)</f>
-        <v>BLF037</v>
+        <v>BLG024</v>
       </c>
       <c r="B19" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!H17),"",'Colar Pedido'!H17)</f>
-        <v>10198819</v>
+        <v>10242292</v>
       </c>
       <c r="C19" s="16">
         <f>IF(ISBLANK('Colar Pedido'!I17),"",VALUE('Colar Pedido'!I17))</f>
-        <v>60</v>
+        <v>400</v>
       </c>
       <c r="D19" s="16" t="str">
         <f>IF(Imprimir!B19="", "", _xlfn.XLOOKUP(VALUE(Imprimir!B19),DB!A:A,DB!B:B,""))</f>
-        <v>SLIVE</v>
+        <v/>
       </c>
       <c r="E19" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!C17),"",'Colar Pedido'!C17)</f>
-        <v>0000118236</v>
+        <v>0000125490</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!E18), "", 'Colar Pedido'!E18)</f>
-        <v>BLD070</v>
+        <v>BLG028</v>
       </c>
       <c r="B20" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!H18),"",'Colar Pedido'!H18)</f>
-        <v>10226359</v>
+        <v>10242292</v>
       </c>
       <c r="C20" s="16">
         <f>IF(ISBLANK('Colar Pedido'!I18),"",VALUE('Colar Pedido'!I18))</f>
-        <v>10</v>
+        <v>400</v>
       </c>
       <c r="D20" s="16" t="str">
         <f>IF(Imprimir!B20="", "", _xlfn.XLOOKUP(VALUE(Imprimir!B20),DB!A:A,DB!B:B,""))</f>
-        <v>BOX</v>
+        <v/>
       </c>
       <c r="E20" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!C18),"",'Colar Pedido'!C18)</f>
-        <v>0000118237</v>
+        <v>0000125491</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!E19), "", 'Colar Pedido'!E19)</f>
-        <v>BLF066</v>
+        <v>BLG028</v>
       </c>
       <c r="B21" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!H19),"",'Colar Pedido'!H19)</f>
-        <v>10226417</v>
+        <v>10242292</v>
       </c>
       <c r="C21" s="16">
         <f>IF(ISBLANK('Colar Pedido'!I19),"",VALUE('Colar Pedido'!I19))</f>
@@ -5730,77 +5173,77 @@
       </c>
       <c r="D21" s="16" t="str">
         <f>IF(Imprimir!B21="", "", _xlfn.XLOOKUP(VALUE(Imprimir!B21),DB!A:A,DB!B:B,""))</f>
-        <v>SLIVE</v>
+        <v/>
       </c>
       <c r="E21" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!C19),"",'Colar Pedido'!C19)</f>
-        <v>0000118238</v>
+        <v>0000125492</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!E20), "", 'Colar Pedido'!E20)</f>
-        <v>BLF068</v>
+        <v>BLE013</v>
       </c>
       <c r="B22" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!H20),"",'Colar Pedido'!H20)</f>
-        <v>10226417</v>
+        <v>10226422</v>
       </c>
       <c r="C22" s="16">
         <f>IF(ISBLANK('Colar Pedido'!I20),"",VALUE('Colar Pedido'!I20))</f>
-        <v>400</v>
+        <v>20</v>
       </c>
       <c r="D22" s="16" t="str">
         <f>IF(Imprimir!B22="", "", _xlfn.XLOOKUP(VALUE(Imprimir!B22),DB!A:A,DB!B:B,""))</f>
-        <v>SLIVE</v>
+        <v>BOX</v>
       </c>
       <c r="E22" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!C20),"",'Colar Pedido'!C20)</f>
-        <v>0000118239</v>
+        <v>0000125493</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!E21), "", 'Colar Pedido'!E21)</f>
-        <v>BLF068</v>
+        <v>BLD081</v>
       </c>
       <c r="B23" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!H21),"",'Colar Pedido'!H21)</f>
-        <v>10226417</v>
+        <v>10226422</v>
       </c>
       <c r="C23" s="16">
         <f>IF(ISBLANK('Colar Pedido'!I21),"",VALUE('Colar Pedido'!I21))</f>
-        <v>400</v>
+        <v>110</v>
       </c>
       <c r="D23" s="16" t="str">
         <f>IF(Imprimir!B23="", "", _xlfn.XLOOKUP(VALUE(Imprimir!B23),DB!A:A,DB!B:B,""))</f>
-        <v>SLIVE</v>
+        <v>BOX</v>
       </c>
       <c r="E23" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!C21),"",'Colar Pedido'!C21)</f>
-        <v>0000118240</v>
+        <v>0000125494</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!E22), "", 'Colar Pedido'!E22)</f>
-        <v>BLG085</v>
+        <v>BLG025</v>
       </c>
       <c r="B24" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!H22),"",'Colar Pedido'!H22)</f>
-        <v>10226454</v>
+        <v>10226374</v>
       </c>
       <c r="C24" s="16">
         <f>IF(ISBLANK('Colar Pedido'!I22),"",VALUE('Colar Pedido'!I22))</f>
-        <v>40</v>
+        <v>270</v>
       </c>
       <c r="D24" s="16" t="str">
         <f>IF(Imprimir!B24="", "", _xlfn.XLOOKUP(VALUE(Imprimir!B24),DB!A:A,DB!B:B,""))</f>
-        <v>BOX</v>
+        <v>NINE</v>
       </c>
       <c r="E24" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!C22),"",'Colar Pedido'!C22)</f>
-        <v>0000118241</v>
+        <v>0000125495</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -5810,165 +5253,165 @@
       </c>
       <c r="B25" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!H23),"",'Colar Pedido'!H23)</f>
-        <v>10226441</v>
+        <v>10226374</v>
       </c>
       <c r="C25" s="16">
         <f>IF(ISBLANK('Colar Pedido'!I23),"",VALUE('Colar Pedido'!I23))</f>
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D25" s="16" t="str">
         <f>IF(Imprimir!B25="", "", _xlfn.XLOOKUP(VALUE(Imprimir!B25),DB!A:A,DB!B:B,""))</f>
-        <v>BOX</v>
+        <v>NINE</v>
       </c>
       <c r="E25" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!C23),"",'Colar Pedido'!C23)</f>
-        <v>0000118242</v>
+        <v>0000125496</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!E24), "", 'Colar Pedido'!E24)</f>
-        <v>BLD088</v>
+        <v>BLF053</v>
       </c>
       <c r="B26" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!H24),"",'Colar Pedido'!H24)</f>
-        <v>10227896</v>
+        <v>10247603</v>
       </c>
       <c r="C26" s="16">
         <f>IF(ISBLANK('Colar Pedido'!I24),"",VALUE('Colar Pedido'!I24))</f>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D26" s="16" t="str">
         <f>IF(Imprimir!B26="", "", _xlfn.XLOOKUP(VALUE(Imprimir!B26),DB!A:A,DB!B:B,""))</f>
-        <v>BOX</v>
+        <v>NINE</v>
       </c>
       <c r="E26" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!C24),"",'Colar Pedido'!C24)</f>
-        <v>0000118243</v>
+        <v>0000125497</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!E25), "", 'Colar Pedido'!E25)</f>
-        <v>BLE032</v>
+        <v>BLG013</v>
       </c>
       <c r="B27" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!H25),"",'Colar Pedido'!H25)</f>
-        <v>10226377</v>
+        <v>10226368</v>
       </c>
       <c r="C27" s="16">
         <f>IF(ISBLANK('Colar Pedido'!I25),"",VALUE('Colar Pedido'!I25))</f>
-        <v>400</v>
+        <v>360</v>
       </c>
       <c r="D27" s="16" t="str">
         <f>IF(Imprimir!B27="", "", _xlfn.XLOOKUP(VALUE(Imprimir!B27),DB!A:A,DB!B:B,""))</f>
-        <v/>
+        <v>NINE</v>
       </c>
       <c r="E27" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!C25),"",'Colar Pedido'!C25)</f>
-        <v>0000118244</v>
+        <v>0000125498</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!E26), "", 'Colar Pedido'!E26)</f>
-        <v>BLF076</v>
+        <v>BLG014</v>
       </c>
       <c r="B28" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!H26),"",'Colar Pedido'!H26)</f>
-        <v>10226403</v>
+        <v>10226368</v>
       </c>
       <c r="C28" s="16">
         <f>IF(ISBLANK('Colar Pedido'!I26),"",VALUE('Colar Pedido'!I26))</f>
-        <v>80</v>
+        <v>360</v>
       </c>
       <c r="D28" s="16" t="str">
         <f>IF(Imprimir!B28="", "", _xlfn.XLOOKUP(VALUE(Imprimir!B28),DB!A:A,DB!B:B,""))</f>
-        <v>SLIVE</v>
+        <v>NINE</v>
       </c>
       <c r="E28" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!C26),"",'Colar Pedido'!C26)</f>
-        <v>0000118245</v>
+        <v>0000125499</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!E27), "", 'Colar Pedido'!E27)</f>
-        <v>BLF061</v>
+        <v>BLF079</v>
       </c>
       <c r="B29" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!H27),"",'Colar Pedido'!H27)</f>
-        <v>10226452</v>
+        <v>10226368</v>
       </c>
       <c r="C29" s="16">
         <f>IF(ISBLANK('Colar Pedido'!I27),"",VALUE('Colar Pedido'!I27))</f>
-        <v>400</v>
+        <v>40</v>
       </c>
       <c r="D29" s="16" t="str">
         <f>IF(Imprimir!B29="", "", _xlfn.XLOOKUP(VALUE(Imprimir!B29),DB!A:A,DB!B:B,""))</f>
-        <v>SLEEVE P</v>
+        <v>NINE</v>
       </c>
       <c r="E29" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!C27),"",'Colar Pedido'!C27)</f>
-        <v>0000118246</v>
+        <v>0000125500</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!E28), "", 'Colar Pedido'!E28)</f>
-        <v>BLE015</v>
+        <v>BLF026</v>
       </c>
       <c r="B30" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!H28),"",'Colar Pedido'!H28)</f>
-        <v>10226452</v>
+        <v>10226367</v>
       </c>
       <c r="C30" s="16">
         <f>IF(ISBLANK('Colar Pedido'!I28),"",VALUE('Colar Pedido'!I28))</f>
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="D30" s="16" t="str">
         <f>IF(Imprimir!B30="", "", _xlfn.XLOOKUP(VALUE(Imprimir!B30),DB!A:A,DB!B:B,""))</f>
-        <v>SLEEVE P</v>
+        <v>NINE</v>
       </c>
       <c r="E30" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!C28),"",'Colar Pedido'!C28)</f>
-        <v>0000118247</v>
+        <v>0000125501</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!E29), "", 'Colar Pedido'!E29)</f>
-        <v>BLH087</v>
+        <v>BLD069</v>
       </c>
       <c r="B31" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!H29),"",'Colar Pedido'!H29)</f>
-        <v>10226452</v>
+        <v>10226398</v>
       </c>
       <c r="C31" s="16">
         <f>IF(ISBLANK('Colar Pedido'!I29),"",VALUE('Colar Pedido'!I29))</f>
-        <v>110</v>
+        <v>240</v>
       </c>
       <c r="D31" s="16" t="str">
         <f>IF(Imprimir!B31="", "", _xlfn.XLOOKUP(VALUE(Imprimir!B31),DB!A:A,DB!B:B,""))</f>
-        <v>SLEEVE P</v>
+        <v>SLIVE</v>
       </c>
       <c r="E31" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!C29),"",'Colar Pedido'!C29)</f>
-        <v>0000118248</v>
+        <v>0000125502</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!E30), "", 'Colar Pedido'!E30)</f>
-        <v>BLE003</v>
+        <v>BLD086</v>
       </c>
       <c r="B32" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!H30),"",'Colar Pedido'!H30)</f>
-        <v>10226420</v>
+        <v>10226398</v>
       </c>
       <c r="C32" s="16">
         <f>IF(ISBLANK('Colar Pedido'!I30),"",VALUE('Colar Pedido'!I30))</f>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D32" s="16" t="str">
         <f>IF(Imprimir!B32="", "", _xlfn.XLOOKUP(VALUE(Imprimir!B32),DB!A:A,DB!B:B,""))</f>
@@ -5976,39 +5419,39 @@
       </c>
       <c r="E32" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!C30),"",'Colar Pedido'!C30)</f>
-        <v>0000118249</v>
+        <v>0000125503</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!E31), "", 'Colar Pedido'!E31)</f>
-        <v>BLG009</v>
+        <v>BLE029</v>
       </c>
       <c r="B33" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!H31),"",'Colar Pedido'!H31)</f>
-        <v>10226380</v>
+        <v>10226398</v>
       </c>
       <c r="C33" s="16">
         <f>IF(ISBLANK('Colar Pedido'!I31),"",VALUE('Colar Pedido'!I31))</f>
-        <v>400</v>
+        <v>40</v>
       </c>
       <c r="D33" s="16" t="str">
         <f>IF(Imprimir!B33="", "", _xlfn.XLOOKUP(VALUE(Imprimir!B33),DB!A:A,DB!B:B,""))</f>
-        <v>BOX</v>
+        <v>SLIVE</v>
       </c>
       <c r="E33" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!C31),"",'Colar Pedido'!C31)</f>
-        <v>0000118250</v>
+        <v>0000125504</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!E32), "", 'Colar Pedido'!E32)</f>
-        <v>BLH052</v>
+        <v>BLF004</v>
       </c>
       <c r="B34" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!H32),"",'Colar Pedido'!H32)</f>
-        <v>10226380</v>
+        <v>10226461</v>
       </c>
       <c r="C34" s="16">
         <f>IF(ISBLANK('Colar Pedido'!I32),"",VALUE('Colar Pedido'!I32))</f>
@@ -6016,65 +5459,65 @@
       </c>
       <c r="D34" s="16" t="str">
         <f>IF(Imprimir!B34="", "", _xlfn.XLOOKUP(VALUE(Imprimir!B34),DB!A:A,DB!B:B,""))</f>
-        <v>BOX</v>
+        <v/>
       </c>
       <c r="E34" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!C32),"",'Colar Pedido'!C32)</f>
-        <v>0000118251</v>
+        <v>0000125505</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!E33), "", 'Colar Pedido'!E33)</f>
-        <v>BLH054</v>
+        <v>BLF004</v>
       </c>
       <c r="B35" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!H33),"",'Colar Pedido'!H33)</f>
-        <v>10226380</v>
+        <v>10226461</v>
       </c>
       <c r="C35" s="16">
         <f>IF(ISBLANK('Colar Pedido'!I33),"",VALUE('Colar Pedido'!I33))</f>
-        <v>340</v>
+        <v>400</v>
       </c>
       <c r="D35" s="16" t="str">
         <f>IF(Imprimir!B35="", "", _xlfn.XLOOKUP(VALUE(Imprimir!B35),DB!A:A,DB!B:B,""))</f>
-        <v>BOX</v>
+        <v/>
       </c>
       <c r="E35" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!C33),"",'Colar Pedido'!C33)</f>
-        <v>0000118252</v>
+        <v>0000125506</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!E34), "", 'Colar Pedido'!E34)</f>
-        <v>BLE024</v>
+        <v>BLF075</v>
       </c>
       <c r="B36" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!H34),"",'Colar Pedido'!H34)</f>
-        <v>10226380</v>
+        <v>10226461</v>
       </c>
       <c r="C36" s="16">
         <f>IF(ISBLANK('Colar Pedido'!I34),"",VALUE('Colar Pedido'!I34))</f>
-        <v>220</v>
+        <v>400</v>
       </c>
       <c r="D36" s="16" t="str">
         <f>IF(Imprimir!B36="", "", _xlfn.XLOOKUP(VALUE(Imprimir!B36),DB!A:A,DB!B:B,""))</f>
-        <v>BOX</v>
+        <v/>
       </c>
       <c r="E36" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!C34),"",'Colar Pedido'!C34)</f>
-        <v>0000118253</v>
+        <v>0000125507</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!E35), "", 'Colar Pedido'!E35)</f>
-        <v>BLH078</v>
+        <v>BLG019</v>
       </c>
       <c r="B37" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!H35),"",'Colar Pedido'!H35)</f>
-        <v>10208005</v>
+        <v>10226373</v>
       </c>
       <c r="C37" s="16">
         <f>IF(ISBLANK('Colar Pedido'!I35),"",VALUE('Colar Pedido'!I35))</f>
@@ -6086,21 +5529,21 @@
       </c>
       <c r="E37" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!C35),"",'Colar Pedido'!C35)</f>
-        <v>0000118254</v>
+        <v>0000125508</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!E36), "", 'Colar Pedido'!E36)</f>
-        <v>BLE045</v>
+        <v>BLG019</v>
       </c>
       <c r="B38" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!H36),"",'Colar Pedido'!H36)</f>
-        <v>10208005</v>
+        <v>10226373</v>
       </c>
       <c r="C38" s="16">
         <f>IF(ISBLANK('Colar Pedido'!I36),"",VALUE('Colar Pedido'!I36))</f>
-        <v>180</v>
+        <v>400</v>
       </c>
       <c r="D38" s="16" t="str">
         <f>IF(Imprimir!B38="", "", _xlfn.XLOOKUP(VALUE(Imprimir!B38),DB!A:A,DB!B:B,""))</f>
@@ -6108,21 +5551,21 @@
       </c>
       <c r="E38" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!C36),"",'Colar Pedido'!C36)</f>
-        <v>0000118255</v>
+        <v>0000125509</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!E37), "", 'Colar Pedido'!E37)</f>
-        <v>BLF079</v>
+        <v>BLG039</v>
       </c>
       <c r="B39" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!H37),"",'Colar Pedido'!H37)</f>
-        <v>10208005</v>
+        <v>10226373</v>
       </c>
       <c r="C39" s="16">
         <f>IF(ISBLANK('Colar Pedido'!I37),"",VALUE('Colar Pedido'!I37))</f>
-        <v>20</v>
+        <v>400</v>
       </c>
       <c r="D39" s="16" t="str">
         <f>IF(Imprimir!B39="", "", _xlfn.XLOOKUP(VALUE(Imprimir!B39),DB!A:A,DB!B:B,""))</f>
@@ -6130,17 +5573,17 @@
       </c>
       <c r="E39" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!C37),"",'Colar Pedido'!C37)</f>
-        <v>0000118256</v>
+        <v>0000125510</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!E38), "", 'Colar Pedido'!E38)</f>
-        <v>BLG084</v>
+        <v>BLG047</v>
       </c>
       <c r="B40" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!H38),"",'Colar Pedido'!H38)</f>
-        <v>10226463</v>
+        <v>10226373</v>
       </c>
       <c r="C40" s="16">
         <f>IF(ISBLANK('Colar Pedido'!I38),"",VALUE('Colar Pedido'!I38))</f>
@@ -6148,179 +5591,179 @@
       </c>
       <c r="D40" s="16" t="str">
         <f>IF(Imprimir!B40="", "", _xlfn.XLOOKUP(VALUE(Imprimir!B40),DB!A:A,DB!B:B,""))</f>
-        <v>SLIVE</v>
+        <v>BOX</v>
       </c>
       <c r="E40" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!C38),"",'Colar Pedido'!C38)</f>
-        <v>0000118257</v>
+        <v>0000125511</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!E39), "", 'Colar Pedido'!E39)</f>
-        <v>BLH074</v>
+        <v>BLG047</v>
       </c>
       <c r="B41" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!H39),"",'Colar Pedido'!H39)</f>
-        <v>10208167</v>
+        <v>10226373</v>
       </c>
       <c r="C41" s="16">
         <f>IF(ISBLANK('Colar Pedido'!I39),"",VALUE('Colar Pedido'!I39))</f>
-        <v>80</v>
+        <v>400</v>
       </c>
       <c r="D41" s="16" t="str">
         <f>IF(Imprimir!B41="", "", _xlfn.XLOOKUP(VALUE(Imprimir!B41),DB!A:A,DB!B:B,""))</f>
-        <v>SLEEVE P</v>
+        <v>BOX</v>
       </c>
       <c r="E41" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!C39),"",'Colar Pedido'!C39)</f>
-        <v>0000118258</v>
+        <v>0000125512</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!E40), "", 'Colar Pedido'!E40)</f>
-        <v>BLE031</v>
+        <v/>
       </c>
       <c r="B42" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!H40),"",'Colar Pedido'!H40)</f>
-        <v>10226367</v>
-      </c>
-      <c r="C42" s="16">
+        <v/>
+      </c>
+      <c r="C42" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!I40),"",VALUE('Colar Pedido'!I40))</f>
-        <v>10</v>
+        <v/>
       </c>
       <c r="D42" s="16" t="str">
         <f>IF(Imprimir!B42="", "", _xlfn.XLOOKUP(VALUE(Imprimir!B42),DB!A:A,DB!B:B,""))</f>
-        <v>NINE</v>
+        <v/>
       </c>
       <c r="E42" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!C40),"",'Colar Pedido'!C40)</f>
-        <v>0000118259</v>
+        <v/>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!E41), "", 'Colar Pedido'!E41)</f>
-        <v>BLF026</v>
+        <v/>
       </c>
       <c r="B43" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!H41),"",'Colar Pedido'!H41)</f>
-        <v>10226367</v>
-      </c>
-      <c r="C43" s="16">
+        <v/>
+      </c>
+      <c r="C43" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!I41),"",VALUE('Colar Pedido'!I41))</f>
-        <v>70</v>
+        <v/>
       </c>
       <c r="D43" s="16" t="str">
         <f>IF(Imprimir!B43="", "", _xlfn.XLOOKUP(VALUE(Imprimir!B43),DB!A:A,DB!B:B,""))</f>
-        <v>NINE</v>
+        <v/>
       </c>
       <c r="E43" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!C41),"",'Colar Pedido'!C41)</f>
-        <v>0000118260</v>
+        <v/>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!E42), "", 'Colar Pedido'!E42)</f>
-        <v>BLF051</v>
+        <v/>
       </c>
       <c r="B44" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!H42),"",'Colar Pedido'!H42)</f>
-        <v>10226388</v>
-      </c>
-      <c r="C44" s="16">
+        <v/>
+      </c>
+      <c r="C44" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!I42),"",VALUE('Colar Pedido'!I42))</f>
-        <v>30</v>
+        <v/>
       </c>
       <c r="D44" s="16" t="str">
         <f>IF(Imprimir!B44="", "", _xlfn.XLOOKUP(VALUE(Imprimir!B44),DB!A:A,DB!B:B,""))</f>
-        <v>BOX</v>
+        <v/>
       </c>
       <c r="E44" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!C42),"",'Colar Pedido'!C42)</f>
-        <v>0000118261</v>
+        <v/>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!E43), "", 'Colar Pedido'!E43)</f>
-        <v>BLG053</v>
+        <v/>
       </c>
       <c r="B45" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!H43),"",'Colar Pedido'!H43)</f>
-        <v>10242293</v>
-      </c>
-      <c r="C45" s="16">
+        <v/>
+      </c>
+      <c r="C45" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!I43),"",VALUE('Colar Pedido'!I43))</f>
-        <v>400</v>
+        <v/>
       </c>
       <c r="D45" s="16" t="str">
         <f>IF(Imprimir!B45="", "", _xlfn.XLOOKUP(VALUE(Imprimir!B45),DB!A:A,DB!B:B,""))</f>
-        <v>BOX</v>
+        <v/>
       </c>
       <c r="E45" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!C43),"",'Colar Pedido'!C43)</f>
-        <v>0000118262</v>
+        <v/>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!E44), "", 'Colar Pedido'!E44)</f>
-        <v>BLG053</v>
+        <v/>
       </c>
       <c r="B46" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!H44),"",'Colar Pedido'!H44)</f>
-        <v>10242293</v>
-      </c>
-      <c r="C46" s="16">
+        <v/>
+      </c>
+      <c r="C46" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!I44),"",VALUE('Colar Pedido'!I44))</f>
-        <v>400</v>
+        <v/>
       </c>
       <c r="D46" s="16" t="str">
         <f>IF(Imprimir!B46="", "", _xlfn.XLOOKUP(VALUE(Imprimir!B46),DB!A:A,DB!B:B,""))</f>
-        <v>BOX</v>
+        <v/>
       </c>
       <c r="E46" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!C44),"",'Colar Pedido'!C44)</f>
-        <v>0000118263</v>
+        <v/>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!E45), "", 'Colar Pedido'!E45)</f>
-        <v>BLF001</v>
+        <v/>
       </c>
       <c r="B47" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!H45),"",'Colar Pedido'!H45)</f>
-        <v>10226404</v>
-      </c>
-      <c r="C47" s="16">
+        <v/>
+      </c>
+      <c r="C47" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!I45),"",VALUE('Colar Pedido'!I45))</f>
-        <v>160</v>
+        <v/>
       </c>
       <c r="D47" s="16" t="str">
         <f>IF(Imprimir!B47="", "", _xlfn.XLOOKUP(VALUE(Imprimir!B47),DB!A:A,DB!B:B,""))</f>
-        <v>BOX</v>
+        <v/>
       </c>
       <c r="E47" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!C45),"",'Colar Pedido'!C45)</f>
-        <v>0000118264</v>
+        <v/>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!E46), "", 'Colar Pedido'!E46)</f>
-        <v>BLE025</v>
+        <v/>
       </c>
       <c r="B48" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!H46),"",'Colar Pedido'!H46)</f>
-        <v>10226461</v>
-      </c>
-      <c r="C48" s="16">
+        <v/>
+      </c>
+      <c r="C48" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!I46),"",VALUE('Colar Pedido'!I46))</f>
-        <v>400</v>
+        <v/>
       </c>
       <c r="D48" s="16" t="str">
         <f>IF(Imprimir!B48="", "", _xlfn.XLOOKUP(VALUE(Imprimir!B48),DB!A:A,DB!B:B,""))</f>
@@ -6328,21 +5771,21 @@
       </c>
       <c r="E48" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!C46),"",'Colar Pedido'!C46)</f>
-        <v>0000118265</v>
+        <v/>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!E47), "", 'Colar Pedido'!E47)</f>
-        <v>BLF002</v>
+        <v/>
       </c>
       <c r="B49" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!H47),"",'Colar Pedido'!H47)</f>
-        <v>10226461</v>
-      </c>
-      <c r="C49" s="16">
+        <v/>
+      </c>
+      <c r="C49" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!I47),"",VALUE('Colar Pedido'!I47))</f>
-        <v>400</v>
+        <v/>
       </c>
       <c r="D49" s="16" t="str">
         <f>IF(Imprimir!B49="", "", _xlfn.XLOOKUP(VALUE(Imprimir!B49),DB!A:A,DB!B:B,""))</f>
@@ -6350,29 +5793,29 @@
       </c>
       <c r="E49" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!C47),"",'Colar Pedido'!C47)</f>
-        <v>0000118266</v>
+        <v/>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!E48), "", 'Colar Pedido'!E48)</f>
-        <v>BLE005</v>
+        <v/>
       </c>
       <c r="B50" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!H48),"",'Colar Pedido'!H48)</f>
-        <v>10226386</v>
-      </c>
-      <c r="C50" s="16">
+        <v/>
+      </c>
+      <c r="C50" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!I48),"",VALUE('Colar Pedido'!I48))</f>
-        <v>200</v>
+        <v/>
       </c>
       <c r="D50" s="16" t="str">
         <f>IF(Imprimir!B50="", "", _xlfn.XLOOKUP(VALUE(Imprimir!B50),DB!A:A,DB!B:B,""))</f>
-        <v>BOX</v>
+        <v/>
       </c>
       <c r="E50" s="16" t="str">
         <f>IF(ISBLANK('Colar Pedido'!C48),"",'Colar Pedido'!C48)</f>
-        <v>0000118267</v>
+        <v/>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
